--- a/modelo-painel-vendas.xlsx
+++ b/modelo-painel-vendas.xlsx
@@ -5,21 +5,19 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip\OneDrive\Área de Trabalho\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip\OneDrive\Área de Trabalho\SALES DASHBOARD - CLAUDE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E581C976-EBF4-44D2-A314-19963A7D798A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061EF26C-AF64-48E8-BA79-9F289E460106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unidades" sheetId="1" r:id="rId1"/>
-    <sheet name="Cadastro de Unidades" sheetId="5" state="hidden" r:id="rId2"/>
-    <sheet name="Corretores" sheetId="4" r:id="rId3"/>
-    <sheet name="Instruções" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="Corretores" sheetId="4" r:id="rId2"/>
+    <sheet name="Instruções" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cadastro de Unidades'!$A$1:$E$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unidades!$A$1:$I$647</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Unidades!$C$1:$H$140</definedName>
   </definedNames>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="179">
   <si>
     <t>Empreendimento</t>
   </si>
@@ -185,12 +183,6 @@
     <t>Base Egecon</t>
   </si>
   <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Descrição</t>
-  </si>
-  <si>
     <t>Loja 1</t>
   </si>
   <si>
@@ -200,27 +192,6 @@
     <t>Loja 3</t>
   </si>
   <si>
-    <t>Loja 4</t>
-  </si>
-  <si>
-    <t>Loja 5</t>
-  </si>
-  <si>
-    <t>Loja 6</t>
-  </si>
-  <si>
-    <t>Loja 7</t>
-  </si>
-  <si>
-    <t>Loja 8</t>
-  </si>
-  <si>
-    <t>Loja 10</t>
-  </si>
-  <si>
-    <t>Loja 11</t>
-  </si>
-  <si>
     <t>Loja 12</t>
   </si>
   <si>
@@ -245,39 +216,9 @@
     <t>Loja 19</t>
   </si>
   <si>
-    <t>Loja 20</t>
-  </si>
-  <si>
-    <t>Loja 21</t>
-  </si>
-  <si>
-    <t>Loja 22</t>
-  </si>
-  <si>
-    <t>Loja 23</t>
-  </si>
-  <si>
-    <t>Loja 24</t>
-  </si>
-  <si>
     <t>Loja 25</t>
   </si>
   <si>
-    <t>Loja 26</t>
-  </si>
-  <si>
-    <t>Loja 27</t>
-  </si>
-  <si>
-    <t>Loja 28</t>
-  </si>
-  <si>
-    <t>Loja 29</t>
-  </si>
-  <si>
-    <t>Loja 30</t>
-  </si>
-  <si>
     <t>Loja 31</t>
   </si>
   <si>
@@ -290,63 +231,9 @@
     <t>Loja 34</t>
   </si>
   <si>
-    <t>102 - BL 1</t>
-  </si>
-  <si>
-    <t>103 - BL 1</t>
-  </si>
-  <si>
-    <t>104 - BL 1</t>
-  </si>
-  <si>
-    <t>105 - BL 1</t>
-  </si>
-  <si>
-    <t>106 - BL 1</t>
-  </si>
-  <si>
-    <t>107 - BL 1</t>
-  </si>
-  <si>
-    <t>109 - BL 1</t>
-  </si>
-  <si>
-    <t>110 - BL 1</t>
-  </si>
-  <si>
     <t>111 - BL 1</t>
   </si>
   <si>
-    <t>201 - BL 1</t>
-  </si>
-  <si>
-    <t>202 - BL 1</t>
-  </si>
-  <si>
-    <t>203 - BL 1</t>
-  </si>
-  <si>
-    <t>204 - BL 1</t>
-  </si>
-  <si>
-    <t>205 - BL 1</t>
-  </si>
-  <si>
-    <t>206 - BL 1</t>
-  </si>
-  <si>
-    <t>207 - BL 1</t>
-  </si>
-  <si>
-    <t>209 - BL 1</t>
-  </si>
-  <si>
-    <t>210 - BL 1</t>
-  </si>
-  <si>
-    <t>211 - BL 1</t>
-  </si>
-  <si>
     <t>301 - BL 1</t>
   </si>
   <si>
@@ -380,126 +267,21 @@
     <t>311 - BL 1</t>
   </si>
   <si>
-    <t>401 - BL 1</t>
-  </si>
-  <si>
-    <t>402 - BL 1</t>
-  </si>
-  <si>
-    <t>403 - BL 1</t>
-  </si>
-  <si>
-    <t>404 - BL 1</t>
-  </si>
-  <si>
-    <t>405 - BL 1</t>
-  </si>
-  <si>
-    <t>406 - BL 1</t>
-  </si>
-  <si>
-    <t>407 - BL 1</t>
-  </si>
-  <si>
-    <t>408 - BL 1</t>
-  </si>
-  <si>
     <t>409 - BL 1</t>
   </si>
   <si>
-    <t>410 - BL 1</t>
-  </si>
-  <si>
-    <t>411 - BL 1</t>
-  </si>
-  <si>
-    <t>501 - BL 1</t>
-  </si>
-  <si>
     <t>503 - BL 1</t>
   </si>
   <si>
-    <t>504 - BL 1</t>
-  </si>
-  <si>
-    <t>505 - BL 1</t>
-  </si>
-  <si>
-    <t>506 - BL 1</t>
-  </si>
-  <si>
-    <t>507 - BL 1</t>
-  </si>
-  <si>
-    <t>508 - BL 1</t>
-  </si>
-  <si>
-    <t>509 - BL 1</t>
-  </si>
-  <si>
-    <t>510 - BL 1</t>
-  </si>
-  <si>
-    <t>511 - BL 1</t>
-  </si>
-  <si>
-    <t>101 - BL 2</t>
-  </si>
-  <si>
-    <t>102 - BL 2</t>
-  </si>
-  <si>
-    <t>103 - BL 2</t>
-  </si>
-  <si>
     <t>104 - BL 2</t>
   </si>
   <si>
     <t>105 - BL 2</t>
   </si>
   <si>
-    <t>106 - BL 2</t>
-  </si>
-  <si>
-    <t>107 - BL 2</t>
-  </si>
-  <si>
-    <t>112 - BL 2</t>
-  </si>
-  <si>
-    <t>201 - BL 2</t>
-  </si>
-  <si>
-    <t>202 - BL 2</t>
-  </si>
-  <si>
-    <t>203 - BL 2</t>
-  </si>
-  <si>
-    <t>204 - BL 2</t>
-  </si>
-  <si>
-    <t>205 - BL 2</t>
-  </si>
-  <si>
-    <t>206 - BL 2</t>
-  </si>
-  <si>
-    <t>207 - BL 2</t>
-  </si>
-  <si>
     <t>208 - BL 2</t>
   </si>
   <si>
-    <t>209 - BL 2</t>
-  </si>
-  <si>
-    <t>211 - BL 2</t>
-  </si>
-  <si>
-    <t>212 - BL 2</t>
-  </si>
-  <si>
     <t>301 - BL 2</t>
   </si>
   <si>
@@ -534,78 +316,6 @@
   </si>
   <si>
     <t>312 - BL 2</t>
-  </si>
-  <si>
-    <t>401 - BL 2</t>
-  </si>
-  <si>
-    <t>402 - BL 2</t>
-  </si>
-  <si>
-    <t>403 - BL 2</t>
-  </si>
-  <si>
-    <t>404 - BL 2</t>
-  </si>
-  <si>
-    <t>405 - BL 2</t>
-  </si>
-  <si>
-    <t>406 - BL 2</t>
-  </si>
-  <si>
-    <t>407 - BL 2</t>
-  </si>
-  <si>
-    <t>408 - BL 2</t>
-  </si>
-  <si>
-    <t>409 - BL 2</t>
-  </si>
-  <si>
-    <t>410 - BL 2</t>
-  </si>
-  <si>
-    <t>411 - BL 2</t>
-  </si>
-  <si>
-    <t>412 - BL 2</t>
-  </si>
-  <si>
-    <t>501 - BL 2</t>
-  </si>
-  <si>
-    <t>502 - BL 2</t>
-  </si>
-  <si>
-    <t>503 - BL 2</t>
-  </si>
-  <si>
-    <t>504 - BL 2</t>
-  </si>
-  <si>
-    <t>505 - BL 2</t>
-  </si>
-  <si>
-    <t>506 - BL 2</t>
-  </si>
-  <si>
-    <t>507 - BL 2</t>
-  </si>
-  <si>
-    <t>508 - BL 2</t>
-  </si>
-  <si>
-    <t>509 - BL 2</t>
-  </si>
-  <si>
-    <t>510 - BL 2</t>
-  </si>
-  <si>
-    <t>511 - BL 2</t>
-  </si>
-  <si>
-    <t>512 - BL 2</t>
   </si>
   <si>
     <t>Permuta</t>
@@ -873,7 +583,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -899,12 +609,6 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -939,7 +643,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -951,17 +655,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1325,46 +1022,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="9" t="s">
-        <v>193</v>
+      <c r="J1" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
+      <c r="A2" s="9">
         <v>44958</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>202</v>
+        <v>106</v>
       </c>
       <c r="D2" s="2">
         <v>101</v>
@@ -1372,8 +1069,8 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="11" t="s">
+      <c r="F2" s="6"/>
+      <c r="G2" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H2" s="3">
@@ -1382,17 +1079,17 @@
       <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="9"/>
+      <c r="J2" s="6"/>
     </row>
     <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="A3" s="9">
         <v>44958</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>202</v>
+        <v>106</v>
       </c>
       <c r="D3" s="2">
         <v>102</v>
@@ -1400,8 +1097,8 @@
       <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H3" s="3">
@@ -1410,17 +1107,17 @@
       <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="9"/>
+      <c r="J3" s="6"/>
     </row>
     <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="9">
         <v>45292</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>202</v>
+        <v>106</v>
       </c>
       <c r="D4" s="2">
         <v>103</v>
@@ -1428,8 +1125,8 @@
       <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="11" t="s">
+      <c r="F4" s="6"/>
+      <c r="G4" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H4" s="3">
@@ -1438,17 +1135,17 @@
       <c r="I4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="9"/>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+      <c r="A5" s="9">
         <v>45352</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>203</v>
+        <v>107</v>
       </c>
       <c r="D5" s="2">
         <v>104</v>
@@ -1456,8 +1153,8 @@
       <c r="E5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="11" t="s">
+      <c r="F5" s="6"/>
+      <c r="G5" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H5" s="3">
@@ -1466,14 +1163,14 @@
       <c r="I5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="9"/>
+      <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+      <c r="A6" s="9">
         <v>44621</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>37</v>
@@ -1484,8 +1181,8 @@
       <c r="E6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="11" t="s">
+      <c r="F6" s="6"/>
+      <c r="G6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H6" s="3">
@@ -1494,17 +1191,17 @@
       <c r="I6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="9"/>
+      <c r="J6" s="6"/>
     </row>
     <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="9">
         <v>44958</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="D7" s="2">
         <v>106</v>
@@ -1512,8 +1209,8 @@
       <c r="E7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="11" t="s">
+      <c r="F7" s="6"/>
+      <c r="G7" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H7" s="3">
@@ -1522,17 +1219,17 @@
       <c r="I7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="9"/>
+      <c r="J7" s="6"/>
     </row>
     <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="A8" s="9">
         <v>44621</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>205</v>
+        <v>109</v>
       </c>
       <c r="D8" s="2">
         <v>201</v>
@@ -1540,8 +1237,8 @@
       <c r="E8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="11" t="s">
+      <c r="F8" s="6"/>
+      <c r="G8" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H8" s="3">
@@ -1550,17 +1247,17 @@
       <c r="I8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="9"/>
+      <c r="J8" s="6"/>
     </row>
     <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="9">
         <v>44652</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>206</v>
+        <v>110</v>
       </c>
       <c r="D9" s="2">
         <v>202</v>
@@ -1568,8 +1265,8 @@
       <c r="E9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="11" t="s">
+      <c r="F9" s="6"/>
+      <c r="G9" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H9" s="3">
@@ -1578,17 +1275,17 @@
       <c r="I9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="9"/>
+      <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="A10" s="9">
         <v>44652</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>207</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2">
         <v>203</v>
@@ -1596,8 +1293,8 @@
       <c r="E10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="11" t="s">
+      <c r="F10" s="6"/>
+      <c r="G10" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H10" s="3">
@@ -1606,17 +1303,17 @@
       <c r="I10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="9"/>
+      <c r="J10" s="6"/>
     </row>
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="A11" s="9">
         <v>45292</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>208</v>
+        <v>112</v>
       </c>
       <c r="D11" s="2">
         <v>204</v>
@@ -1624,8 +1321,8 @@
       <c r="E11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="11" t="s">
+      <c r="F11" s="6"/>
+      <c r="G11" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H11" s="3">
@@ -1634,17 +1331,17 @@
       <c r="I11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J11" s="9"/>
+      <c r="J11" s="6"/>
     </row>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+      <c r="A12" s="9">
         <v>44927</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>209</v>
+        <v>113</v>
       </c>
       <c r="D12" s="2">
         <v>205</v>
@@ -1652,8 +1349,8 @@
       <c r="E12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="11" t="s">
+      <c r="F12" s="6"/>
+      <c r="G12" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H12" s="3">
@@ -1662,17 +1359,17 @@
       <c r="I12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J12" s="9"/>
+      <c r="J12" s="6"/>
     </row>
     <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+      <c r="A13" s="9">
         <v>45292</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>210</v>
+        <v>114</v>
       </c>
       <c r="D13" s="2">
         <v>206</v>
@@ -1680,8 +1377,8 @@
       <c r="E13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="11" t="s">
+      <c r="F13" s="6"/>
+      <c r="G13" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H13" s="3">
@@ -1690,17 +1387,17 @@
       <c r="I13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J13" s="9"/>
+      <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
+      <c r="A14" s="9">
         <v>45231</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>211</v>
+        <v>115</v>
       </c>
       <c r="D14" s="2">
         <v>207</v>
@@ -1708,8 +1405,8 @@
       <c r="E14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="9"/>
-      <c r="G14" s="11" t="s">
+      <c r="F14" s="6"/>
+      <c r="G14" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H14" s="3">
@@ -1718,17 +1415,17 @@
       <c r="I14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J14" s="9"/>
+      <c r="J14" s="6"/>
     </row>
     <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
+      <c r="A15" s="9">
         <v>44866</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>212</v>
+        <v>116</v>
       </c>
       <c r="D15" s="2">
         <v>301</v>
@@ -1736,8 +1433,8 @@
       <c r="E15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="11" t="s">
+      <c r="F15" s="6"/>
+      <c r="G15" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="3">
@@ -1746,17 +1443,17 @@
       <c r="I15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="9"/>
+      <c r="J15" s="6"/>
     </row>
     <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
+      <c r="A16" s="9">
         <v>44621</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>213</v>
+        <v>117</v>
       </c>
       <c r="D16" s="2">
         <v>303</v>
@@ -1764,8 +1461,8 @@
       <c r="E16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="11" t="s">
+      <c r="F16" s="6"/>
+      <c r="G16" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H16" s="3">
@@ -1774,14 +1471,14 @@
       <c r="I16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J16" s="9"/>
+      <c r="J16" s="6"/>
     </row>
     <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
+      <c r="A17" s="9">
         <v>44621</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>37</v>
@@ -1792,8 +1489,8 @@
       <c r="E17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="11" t="s">
+      <c r="F17" s="6"/>
+      <c r="G17" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H17" s="3">
@@ -1802,17 +1499,17 @@
       <c r="I17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J17" s="9"/>
+      <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
+      <c r="A18" s="9">
         <v>44927</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>214</v>
+        <v>118</v>
       </c>
       <c r="D18" s="2">
         <v>307</v>
@@ -1820,8 +1517,8 @@
       <c r="E18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="11" t="s">
+      <c r="F18" s="6"/>
+      <c r="G18" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="3">
@@ -1830,17 +1527,17 @@
       <c r="I18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J18" s="9"/>
+      <c r="J18" s="6"/>
     </row>
     <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
+      <c r="A19" s="9">
         <v>44621</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>215</v>
+        <v>119</v>
       </c>
       <c r="D19" s="2">
         <v>401</v>
@@ -1848,8 +1545,8 @@
       <c r="E19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="11" t="s">
+      <c r="F19" s="6"/>
+      <c r="G19" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H19" s="3">
@@ -1858,17 +1555,17 @@
       <c r="I19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J19" s="9"/>
+      <c r="J19" s="6"/>
     </row>
     <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
+      <c r="A20" s="9">
         <v>44621</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="D20" s="2">
         <v>402</v>
@@ -1876,8 +1573,8 @@
       <c r="E20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="11" t="s">
+      <c r="F20" s="6"/>
+      <c r="G20" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H20" s="3">
@@ -1886,17 +1583,17 @@
       <c r="I20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J20" s="9"/>
+      <c r="J20" s="6"/>
     </row>
     <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
+      <c r="A21" s="9">
         <v>44682</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>217</v>
+        <v>121</v>
       </c>
       <c r="D21" s="2">
         <v>403</v>
@@ -1904,8 +1601,8 @@
       <c r="E21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="11" t="s">
+      <c r="F21" s="6"/>
+      <c r="G21" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H21" s="3">
@@ -1914,17 +1611,17 @@
       <c r="I21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J21" s="9"/>
+      <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
+      <c r="A22" s="9">
         <v>44621</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>218</v>
+        <v>122</v>
       </c>
       <c r="D22" s="2">
         <v>404</v>
@@ -1932,8 +1629,8 @@
       <c r="E22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="11" t="s">
+      <c r="F22" s="6"/>
+      <c r="G22" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H22" s="3">
@@ -1942,17 +1639,17 @@
       <c r="I22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J22" s="9"/>
+      <c r="J22" s="6"/>
     </row>
     <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
+      <c r="A23" s="9">
         <v>44774</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>218</v>
+        <v>122</v>
       </c>
       <c r="D23" s="2">
         <v>405</v>
@@ -1960,8 +1657,8 @@
       <c r="E23" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="11" t="s">
+      <c r="F23" s="6"/>
+      <c r="G23" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H23" s="3">
@@ -1970,17 +1667,17 @@
       <c r="I23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J23" s="9"/>
+      <c r="J23" s="6"/>
     </row>
     <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12">
+      <c r="A24" s="9">
         <v>44896</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>219</v>
+        <v>123</v>
       </c>
       <c r="D24" s="2">
         <v>406</v>
@@ -1988,8 +1685,8 @@
       <c r="E24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="11" t="s">
+      <c r="F24" s="6"/>
+      <c r="G24" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H24" s="3">
@@ -1998,17 +1695,17 @@
       <c r="I24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J24" s="9"/>
+      <c r="J24" s="6"/>
     </row>
     <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
+      <c r="A25" s="9">
         <v>44927</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="D25" s="2">
         <v>407</v>
@@ -2016,8 +1713,8 @@
       <c r="E25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="11" t="s">
+      <c r="F25" s="6"/>
+      <c r="G25" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H25" s="3">
@@ -2026,17 +1723,17 @@
       <c r="I25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J25" s="9"/>
+      <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
+      <c r="A26" s="9">
         <v>44835</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>221</v>
+        <v>125</v>
       </c>
       <c r="D26" s="2">
         <v>502</v>
@@ -2044,8 +1741,8 @@
       <c r="E26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="11" t="s">
+      <c r="F26" s="6"/>
+      <c r="G26" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H26" s="3">
@@ -2054,17 +1751,17 @@
       <c r="I26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J26" s="9"/>
+      <c r="J26" s="6"/>
     </row>
     <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
+      <c r="A27" s="9">
         <v>45139</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>221</v>
+        <v>125</v>
       </c>
       <c r="D27" s="2">
         <v>503</v>
@@ -2072,8 +1769,8 @@
       <c r="E27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="11" t="s">
+      <c r="F27" s="6"/>
+      <c r="G27" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H27" s="3">
@@ -2082,14 +1779,14 @@
       <c r="I27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J27" s="9"/>
+      <c r="J27" s="6"/>
     </row>
     <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12">
+      <c r="A28" s="9">
         <v>44958</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>27</v>
@@ -2100,8 +1797,8 @@
       <c r="E28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F28" s="9"/>
-      <c r="G28" s="11" t="s">
+      <c r="F28" s="6"/>
+      <c r="G28" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H28" s="3">
@@ -2110,26 +1807,26 @@
       <c r="I28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J28" s="9"/>
+      <c r="J28" s="6"/>
     </row>
     <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
+      <c r="A29" s="9">
         <v>45352</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>203</v>
+        <v>107</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>271</v>
+        <v>175</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="11" t="s">
+      <c r="F29" s="6"/>
+      <c r="G29" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H29" s="3">
@@ -2138,17 +1835,17 @@
       <c r="I29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J29" s="9"/>
+      <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="12">
+      <c r="A30" s="9">
         <v>45406</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>222</v>
+        <v>126</v>
       </c>
       <c r="D30" s="2">
         <v>102</v>
@@ -2156,8 +1853,8 @@
       <c r="E30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="11" t="s">
+      <c r="F30" s="6"/>
+      <c r="G30" s="8" t="s">
         <v>26</v>
       </c>
       <c r="H30" s="3">
@@ -2166,17 +1863,17 @@
       <c r="I30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J30" s="9"/>
+      <c r="J30" s="6"/>
     </row>
     <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12">
+      <c r="A31" s="9">
         <v>45352</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>223</v>
+        <v>127</v>
       </c>
       <c r="D31" s="2">
         <v>203</v>
@@ -2184,8 +1881,8 @@
       <c r="E31" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="11" t="s">
+      <c r="F31" s="6"/>
+      <c r="G31" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H31" s="3">
@@ -2194,17 +1891,17 @@
       <c r="I31" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J31" s="9"/>
+      <c r="J31" s="6"/>
     </row>
     <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
+      <c r="A32" s="9">
         <v>45387</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>224</v>
+        <v>128</v>
       </c>
       <c r="D32" s="2">
         <v>205</v>
@@ -2212,8 +1909,8 @@
       <c r="E32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F32" s="9"/>
-      <c r="G32" s="11" t="s">
+      <c r="F32" s="6"/>
+      <c r="G32" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H32" s="3">
@@ -2222,17 +1919,17 @@
       <c r="I32" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J32" s="9"/>
+      <c r="J32" s="6"/>
     </row>
     <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12">
+      <c r="A33" s="9">
         <v>45323</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>225</v>
+        <v>129</v>
       </c>
       <c r="D33" s="2">
         <v>206</v>
@@ -2240,8 +1937,8 @@
       <c r="E33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F33" s="9"/>
-      <c r="G33" s="11" t="s">
+      <c r="F33" s="6"/>
+      <c r="G33" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H33" s="3">
@@ -2250,17 +1947,17 @@
       <c r="I33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J33" s="9"/>
+      <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="12">
+      <c r="A34" s="9">
         <v>45352</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>226</v>
+        <v>130</v>
       </c>
       <c r="D34" s="2">
         <v>404</v>
@@ -2268,25 +1965,25 @@
       <c r="E34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="9"/>
-      <c r="G34" s="11"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="8"/>
       <c r="H34" s="3">
         <v>1240000</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J34" s="9"/>
+      <c r="J34" s="6"/>
     </row>
     <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="12">
+      <c r="A35" s="9">
         <v>45386</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>227</v>
+        <v>131</v>
       </c>
       <c r="D35" s="2">
         <v>502</v>
@@ -2294,25 +1991,25 @@
       <c r="E35" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="9"/>
-      <c r="G35" s="11"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="8"/>
       <c r="H35" s="3">
         <v>1755000</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J35" s="9"/>
+      <c r="J35" s="6"/>
     </row>
     <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="12">
+      <c r="A36" s="9">
         <v>45323</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>228</v>
+        <v>132</v>
       </c>
       <c r="D36" s="2">
         <v>511</v>
@@ -2320,25 +2017,25 @@
       <c r="E36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F36" s="9"/>
-      <c r="G36" s="11"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="8"/>
       <c r="H36" s="3">
         <v>800000</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J36" s="9"/>
+      <c r="J36" s="6"/>
     </row>
     <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="12">
+      <c r="A37" s="9">
         <v>45352</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>229</v>
+        <v>133</v>
       </c>
       <c r="D37" s="2">
         <v>103</v>
@@ -2346,25 +2043,25 @@
       <c r="E37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="9"/>
-      <c r="G37" s="11"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="8"/>
       <c r="H37" s="3">
         <v>800000</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J37" s="9"/>
+      <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="12">
+      <c r="A38" s="9">
         <v>45413</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>274</v>
+        <v>178</v>
       </c>
       <c r="D38" s="2">
         <v>301</v>
@@ -2372,8 +2069,8 @@
       <c r="E38" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="11" t="s">
+      <c r="F38" s="6"/>
+      <c r="G38" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H38" s="3">
@@ -2382,17 +2079,17 @@
       <c r="I38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J38" s="9"/>
+      <c r="J38" s="6"/>
     </row>
     <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="12">
+      <c r="A39" s="9">
         <v>45413</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>230</v>
+        <v>134</v>
       </c>
       <c r="D39" s="2">
         <v>403</v>
@@ -2400,8 +2097,8 @@
       <c r="E39" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="11" t="s">
+      <c r="F39" s="6"/>
+      <c r="G39" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H39" s="3">
@@ -2410,17 +2107,17 @@
       <c r="I39" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J39" s="9"/>
+      <c r="J39" s="6"/>
     </row>
     <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="12">
+      <c r="A40" s="9">
         <v>45413</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>273</v>
+        <v>177</v>
       </c>
       <c r="D40" s="2">
         <v>306</v>
@@ -2428,8 +2125,8 @@
       <c r="E40" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="9"/>
-      <c r="G40" s="11" t="s">
+      <c r="F40" s="6"/>
+      <c r="G40" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H40" s="3">
@@ -2438,17 +2135,17 @@
       <c r="I40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J40" s="9"/>
+      <c r="J40" s="6"/>
     </row>
     <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="12">
+      <c r="A41" s="9">
         <v>45474</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>231</v>
+        <v>135</v>
       </c>
       <c r="D41" s="2">
         <v>504</v>
@@ -2456,8 +2153,8 @@
       <c r="E41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="9"/>
-      <c r="G41" s="11" t="s">
+      <c r="F41" s="6"/>
+      <c r="G41" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H41" s="3">
@@ -2466,17 +2163,17 @@
       <c r="I41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J41" s="9"/>
+      <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="12">
+      <c r="A42" s="9">
         <v>45499</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>232</v>
+        <v>136</v>
       </c>
       <c r="D42" s="2">
         <v>110</v>
@@ -2484,25 +2181,25 @@
       <c r="E42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="11"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="8"/>
       <c r="H42" s="3">
         <v>815000</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J42" s="9"/>
+      <c r="J42" s="6"/>
     </row>
     <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="12">
+      <c r="A43" s="9">
         <v>45534</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>233</v>
+        <v>137</v>
       </c>
       <c r="D43" s="2">
         <v>401</v>
@@ -2510,25 +2207,25 @@
       <c r="E43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="11"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="8"/>
       <c r="H43" s="3">
         <v>695000</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J43" s="9"/>
+      <c r="J43" s="6"/>
     </row>
     <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="12">
+      <c r="A44" s="9">
         <v>45579</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>234</v>
+        <v>138</v>
       </c>
       <c r="D44" s="2">
         <v>405</v>
@@ -2536,8 +2233,8 @@
       <c r="E44" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="9"/>
-      <c r="G44" s="11" t="s">
+      <c r="F44" s="6"/>
+      <c r="G44" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H44" s="3">
@@ -2546,17 +2243,17 @@
       <c r="I44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J44" s="9"/>
+      <c r="J44" s="6"/>
     </row>
     <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="12">
+      <c r="A45" s="9">
         <v>45573</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>235</v>
+        <v>139</v>
       </c>
       <c r="D45" s="2">
         <v>408</v>
@@ -2564,8 +2261,8 @@
       <c r="E45" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="9"/>
-      <c r="G45" s="11" t="s">
+      <c r="F45" s="6"/>
+      <c r="G45" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H45" s="3">
@@ -2574,17 +2271,17 @@
       <c r="I45" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J45" s="9"/>
+      <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="12">
+      <c r="A46" s="9">
         <v>45576</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>236</v>
+        <v>140</v>
       </c>
       <c r="D46" s="2">
         <v>411</v>
@@ -2592,8 +2289,8 @@
       <c r="E46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F46" s="9"/>
-      <c r="G46" s="11" t="s">
+      <c r="F46" s="6"/>
+      <c r="G46" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H46" s="3">
@@ -2602,17 +2299,17 @@
       <c r="I46" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J46" s="9"/>
+      <c r="J46" s="6"/>
     </row>
     <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="12">
+      <c r="A47" s="9">
         <v>45566</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="D47" s="2">
         <v>104</v>
@@ -2620,8 +2317,8 @@
       <c r="E47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="9"/>
-      <c r="G47" s="11" t="s">
+      <c r="F47" s="6"/>
+      <c r="G47" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H47" s="3">
@@ -2630,17 +2327,17 @@
       <c r="I47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J47" s="9"/>
+      <c r="J47" s="6"/>
     </row>
     <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="12">
+      <c r="A48" s="9">
         <v>45566</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="D48" s="2">
         <v>204</v>
@@ -2648,8 +2345,8 @@
       <c r="E48" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F48" s="9"/>
-      <c r="G48" s="11" t="s">
+      <c r="F48" s="6"/>
+      <c r="G48" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H48" s="3">
@@ -2658,17 +2355,17 @@
       <c r="I48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J48" s="9"/>
+      <c r="J48" s="6"/>
     </row>
     <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="12">
+      <c r="A49" s="9">
         <v>45581</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>238</v>
+        <v>142</v>
       </c>
       <c r="D49" s="2">
         <v>406</v>
@@ -2676,8 +2373,8 @@
       <c r="E49" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F49" s="9"/>
-      <c r="G49" s="11" t="s">
+      <c r="F49" s="6"/>
+      <c r="G49" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H49" s="3">
@@ -2686,17 +2383,17 @@
       <c r="I49" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J49" s="9"/>
+      <c r="J49" s="6"/>
     </row>
     <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="12">
+      <c r="A50" s="9">
         <v>45603</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>239</v>
+        <v>143</v>
       </c>
       <c r="D50" s="2">
         <v>501</v>
@@ -2704,8 +2401,8 @@
       <c r="E50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="9"/>
-      <c r="G50" s="11" t="s">
+      <c r="F50" s="6"/>
+      <c r="G50" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H50" s="3">
@@ -2714,17 +2411,17 @@
       <c r="I50" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J50" s="9"/>
+      <c r="J50" s="6"/>
     </row>
     <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="12">
+      <c r="A51" s="9">
         <v>45644</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="D51" s="2">
         <v>304</v>
@@ -2732,8 +2429,8 @@
       <c r="E51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F51" s="9"/>
-      <c r="G51" s="11" t="s">
+      <c r="F51" s="6"/>
+      <c r="G51" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H51" s="3">
@@ -2742,17 +2439,17 @@
       <c r="I51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J51" s="9"/>
+      <c r="J51" s="6"/>
     </row>
     <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="12">
+      <c r="A52" s="9">
         <v>45659</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>241</v>
+        <v>145</v>
       </c>
       <c r="D52" s="2">
         <v>510</v>
@@ -2760,8 +2457,8 @@
       <c r="E52" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="9"/>
-      <c r="G52" s="11" t="s">
+      <c r="F52" s="6"/>
+      <c r="G52" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H52" s="3">
@@ -2770,17 +2467,17 @@
       <c r="I52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J52" s="9"/>
+      <c r="J52" s="6"/>
     </row>
     <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="12">
+      <c r="A53" s="9">
         <v>45659</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>242</v>
+        <v>146</v>
       </c>
       <c r="D53" s="2">
         <v>410</v>
@@ -2788,8 +2485,8 @@
       <c r="E53" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F53" s="9"/>
-      <c r="G53" s="11" t="s">
+      <c r="F53" s="6"/>
+      <c r="G53" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H53" s="3">
@@ -2798,17 +2495,17 @@
       <c r="I53" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J53" s="9"/>
+      <c r="J53" s="6"/>
     </row>
     <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="12">
+      <c r="A54" s="9">
         <v>45659</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>205</v>
+        <v>109</v>
       </c>
       <c r="D54" s="2">
         <v>107</v>
@@ -2816,25 +2513,25 @@
       <c r="E54" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F54" s="9"/>
-      <c r="G54" s="11"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="8"/>
       <c r="H54" s="3">
         <v>770000</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J54" s="9"/>
+      <c r="J54" s="6"/>
     </row>
     <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="12">
+      <c r="A55" s="9">
         <v>45679</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>243</v>
+        <v>147</v>
       </c>
       <c r="D55" s="2">
         <v>505</v>
@@ -2842,8 +2539,8 @@
       <c r="E55" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F55" s="9"/>
-      <c r="G55" s="11" t="s">
+      <c r="F55" s="6"/>
+      <c r="G55" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H55" s="3">
@@ -2852,17 +2549,17 @@
       <c r="I55" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J55" s="9"/>
+      <c r="J55" s="6"/>
     </row>
     <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="12">
+      <c r="A56" s="9">
         <v>45713</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>244</v>
+        <v>148</v>
       </c>
       <c r="D56" s="2">
         <v>308</v>
@@ -2870,8 +2567,8 @@
       <c r="E56" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F56" s="9"/>
-      <c r="G56" s="11" t="s">
+      <c r="F56" s="6"/>
+      <c r="G56" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H56" s="3">
@@ -2880,17 +2577,17 @@
       <c r="I56" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J56" s="9"/>
+      <c r="J56" s="6"/>
     </row>
     <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="12">
+      <c r="A57" s="9">
         <v>45726</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>245</v>
+        <v>149</v>
       </c>
       <c r="D57" s="2">
         <v>309</v>
@@ -2898,8 +2595,8 @@
       <c r="E57" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F57" s="9"/>
-      <c r="G57" s="11" t="s">
+      <c r="F57" s="6"/>
+      <c r="G57" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H57" s="3">
@@ -2908,17 +2605,17 @@
       <c r="I57" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J57" s="9"/>
+      <c r="J57" s="6"/>
     </row>
     <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="12">
+      <c r="A58" s="9">
         <v>45724</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>246</v>
+        <v>150</v>
       </c>
       <c r="D58" s="2">
         <v>506</v>
@@ -2926,8 +2623,8 @@
       <c r="E58" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F58" s="9"/>
-      <c r="G58" s="11" t="s">
+      <c r="F58" s="6"/>
+      <c r="G58" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H58" s="3">
@@ -2936,17 +2633,17 @@
       <c r="I58" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J58" s="9"/>
+      <c r="J58" s="6"/>
     </row>
     <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="12">
+      <c r="A59" s="9">
         <v>45726</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>247</v>
+        <v>151</v>
       </c>
       <c r="D59" s="2">
         <v>512</v>
@@ -2954,8 +2651,8 @@
       <c r="E59" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="9"/>
-      <c r="G59" s="11" t="s">
+      <c r="F59" s="6"/>
+      <c r="G59" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H59" s="3">
@@ -2964,17 +2661,17 @@
       <c r="I59" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J59" s="9"/>
+      <c r="J59" s="6"/>
     </row>
     <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="12">
+      <c r="A60" s="9">
         <v>45738</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>248</v>
+        <v>152</v>
       </c>
       <c r="D60" s="2">
         <v>208</v>
@@ -2982,8 +2679,8 @@
       <c r="E60" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F60" s="9"/>
-      <c r="G60" s="11" t="s">
+      <c r="F60" s="6"/>
+      <c r="G60" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H60" s="3">
@@ -2992,17 +2689,17 @@
       <c r="I60" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J60" s="9"/>
+      <c r="J60" s="6"/>
     </row>
     <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="12">
+      <c r="A61" s="9">
         <v>45783</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>249</v>
+        <v>153</v>
       </c>
       <c r="D61" s="2">
         <v>310</v>
@@ -3010,8 +2707,8 @@
       <c r="E61" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F61" s="9"/>
-      <c r="G61" s="11" t="s">
+      <c r="F61" s="6"/>
+      <c r="G61" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H61" s="3">
@@ -3020,17 +2717,17 @@
       <c r="I61" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J61" s="9"/>
+      <c r="J61" s="6"/>
     </row>
     <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="12">
+      <c r="A62" s="9">
         <v>45860</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="D62" s="2">
         <v>409</v>
@@ -3038,25 +2735,25 @@
       <c r="E62" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="9"/>
-      <c r="G62" s="11"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="8"/>
       <c r="H62" s="3">
         <v>720000</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J62" s="9"/>
+      <c r="J62" s="6"/>
     </row>
     <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="12">
+      <c r="A63" s="9">
         <v>45888</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>250</v>
+        <v>154</v>
       </c>
       <c r="D63" s="2">
         <v>106</v>
@@ -3064,25 +2761,25 @@
       <c r="E63" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F63" s="9"/>
-      <c r="G63" s="11"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="8"/>
       <c r="H63" s="3">
         <v>635000</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J63" s="9"/>
+      <c r="J63" s="6"/>
     </row>
     <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="12">
+      <c r="A64" s="9">
         <v>45909</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>251</v>
+        <v>155</v>
       </c>
       <c r="D64" s="2">
         <v>201</v>
@@ -3090,8 +2787,8 @@
       <c r="E64" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F64" s="9"/>
-      <c r="G64" s="11" t="s">
+      <c r="F64" s="6"/>
+      <c r="G64" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H64" s="3">
@@ -3100,17 +2797,17 @@
       <c r="I64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J64" s="9"/>
+      <c r="J64" s="6"/>
     </row>
     <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="12">
+      <c r="A65" s="9">
         <v>45909</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>251</v>
+        <v>155</v>
       </c>
       <c r="D65" s="2">
         <v>202</v>
@@ -3118,8 +2815,8 @@
       <c r="E65" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="9"/>
-      <c r="G65" s="11" t="s">
+      <c r="F65" s="6"/>
+      <c r="G65" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H65" s="3">
@@ -3128,17 +2825,17 @@
       <c r="I65" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J65" s="9"/>
+      <c r="J65" s="6"/>
     </row>
     <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="12">
+      <c r="A66" s="9">
         <v>45954</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>252</v>
+        <v>156</v>
       </c>
       <c r="D66" s="2">
         <v>210</v>
@@ -3146,25 +2843,25 @@
       <c r="E66" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F66" s="9"/>
-      <c r="G66" s="11"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="8"/>
       <c r="H66" s="3">
         <v>945000</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J66" s="9"/>
+      <c r="J66" s="6"/>
     </row>
     <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="12">
+      <c r="A67" s="9">
         <v>45966</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>253</v>
+        <v>157</v>
       </c>
       <c r="D67" s="2">
         <v>508</v>
@@ -3172,8 +2869,8 @@
       <c r="E67" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F67" s="9"/>
-      <c r="G67" s="11" t="s">
+      <c r="F67" s="6"/>
+      <c r="G67" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H67" s="3">
@@ -3182,17 +2879,17 @@
       <c r="I67" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J67" s="9"/>
+      <c r="J67" s="6"/>
     </row>
     <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="12">
+      <c r="A68" s="9">
         <v>46028</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>254</v>
+        <v>158</v>
       </c>
       <c r="D68" s="2">
         <v>109</v>
@@ -3200,25 +2897,25 @@
       <c r="E68" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F68" s="9"/>
-      <c r="G68" s="11"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="8"/>
       <c r="H68" s="3">
         <v>680000</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J68" s="9"/>
+      <c r="J68" s="6"/>
     </row>
     <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="12">
+      <c r="A69" s="9">
         <v>46031</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>222</v>
+        <v>126</v>
       </c>
       <c r="D69" s="2">
         <v>209</v>
@@ -3226,25 +2923,25 @@
       <c r="E69" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="9"/>
-      <c r="G69" s="11"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="8"/>
       <c r="H69" s="3">
         <v>695000</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J69" s="9"/>
+      <c r="J69" s="6"/>
     </row>
     <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="12">
+      <c r="A70" s="9">
         <v>46034</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>255</v>
+        <v>159</v>
       </c>
       <c r="D70" s="2">
         <v>412</v>
@@ -3252,8 +2949,8 @@
       <c r="E70" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F70" s="9"/>
-      <c r="G70" s="11" t="s">
+      <c r="F70" s="6"/>
+      <c r="G70" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H70" s="3">
@@ -3262,17 +2959,17 @@
       <c r="I70" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J70" s="9"/>
+      <c r="J70" s="6"/>
     </row>
     <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="12">
+      <c r="A71" s="9">
         <v>46036</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>256</v>
+        <v>160</v>
       </c>
       <c r="D71" s="2">
         <v>212</v>
@@ -3280,8 +2977,8 @@
       <c r="E71" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F71" s="9"/>
-      <c r="G71" s="11" t="s">
+      <c r="F71" s="6"/>
+      <c r="G71" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H71" s="3">
@@ -3290,17 +2987,17 @@
       <c r="I71" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J71" s="9"/>
+      <c r="J71" s="6"/>
     </row>
     <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="12">
+      <c r="A72" s="9">
         <v>46038</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="D72" s="2">
         <v>507</v>
@@ -3308,25 +3005,25 @@
       <c r="E72" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F72" s="9"/>
-      <c r="G72" s="11"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="8"/>
       <c r="H72" s="3">
         <v>895000</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J72" s="9"/>
+      <c r="J72" s="6"/>
     </row>
     <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="12">
+      <c r="A73" s="9">
         <v>46032</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>258</v>
+        <v>162</v>
       </c>
       <c r="D73" s="2">
         <v>401</v>
@@ -3334,8 +3031,8 @@
       <c r="E73" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F73" s="9"/>
-      <c r="G73" s="11" t="s">
+      <c r="F73" s="6"/>
+      <c r="G73" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H73" s="3">
@@ -3344,17 +3041,17 @@
       <c r="I73" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J73" s="9"/>
+      <c r="J73" s="6"/>
     </row>
     <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="12">
+      <c r="A74" s="9">
         <v>46043</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>259</v>
+        <v>163</v>
       </c>
       <c r="D74" s="2">
         <v>302</v>
@@ -3362,8 +3059,8 @@
       <c r="E74" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F74" s="9"/>
-      <c r="G74" s="11" t="s">
+      <c r="F74" s="6"/>
+      <c r="G74" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H74" s="3">
@@ -3372,17 +3069,17 @@
       <c r="I74" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J74" s="9"/>
+      <c r="J74" s="6"/>
     </row>
     <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="12">
+      <c r="A75" s="9">
         <v>46060</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>198</v>
+        <v>102</v>
       </c>
       <c r="D75" s="2">
         <v>101</v>
@@ -3390,8 +3087,8 @@
       <c r="E75" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F75" s="9"/>
-      <c r="G75" s="11" t="s">
+      <c r="F75" s="6"/>
+      <c r="G75" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H75" s="3">
@@ -3400,17 +3097,17 @@
       <c r="I75" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J75" s="9"/>
+      <c r="J75" s="6"/>
     </row>
     <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="12">
+      <c r="A76" s="9">
         <v>46045</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>260</v>
+        <v>164</v>
       </c>
       <c r="D76" s="2">
         <v>105</v>
@@ -3418,8 +3115,8 @@
       <c r="E76" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F76" s="9"/>
-      <c r="G76" s="11" t="s">
+      <c r="F76" s="6"/>
+      <c r="G76" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H76" s="3">
@@ -3428,17 +3125,17 @@
       <c r="I76" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J76" s="9"/>
+      <c r="J76" s="6"/>
     </row>
     <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="12">
+      <c r="A77" s="9">
         <v>46058</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>261</v>
+        <v>165</v>
       </c>
       <c r="D77" s="2">
         <v>509</v>
@@ -3446,25 +3143,25 @@
       <c r="E77" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="9"/>
-      <c r="G77" s="11"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="8"/>
       <c r="H77" s="3">
         <v>775000</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J77" s="9"/>
+      <c r="J77" s="6"/>
     </row>
     <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="12">
+      <c r="A78" s="9">
         <v>46083</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>262</v>
+        <v>166</v>
       </c>
       <c r="D78" s="2">
         <v>207</v>
@@ -3472,8 +3169,8 @@
       <c r="E78" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F78" s="9"/>
-      <c r="G78" s="11" t="s">
+      <c r="F78" s="6"/>
+      <c r="G78" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H78" s="3">
@@ -3482,17 +3179,17 @@
       <c r="I78" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J78" s="9"/>
+      <c r="J78" s="6"/>
     </row>
     <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="12">
+      <c r="A79" s="9">
         <v>46107</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>263</v>
+        <v>167</v>
       </c>
       <c r="D79" s="2">
         <v>211</v>
@@ -3500,25 +3197,25 @@
       <c r="E79" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F79" s="9"/>
-      <c r="G79" s="11"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="8"/>
       <c r="H79" s="3">
         <v>905000</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J79" s="9"/>
+      <c r="J79" s="6"/>
     </row>
     <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="12">
+      <c r="A80" s="9">
         <v>46120</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="D80" s="2">
         <v>407</v>
@@ -3526,8 +3223,8 @@
       <c r="E80" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F80" s="9"/>
-      <c r="G80" s="11" t="s">
+      <c r="F80" s="6"/>
+      <c r="G80" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H80" s="3">
@@ -3536,17 +3233,17 @@
       <c r="I80" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J80" s="9"/>
+      <c r="J80" s="6"/>
     </row>
     <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="12">
+      <c r="A81" s="9">
         <v>46090</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>265</v>
+        <v>169</v>
       </c>
       <c r="D81" s="2">
         <v>108</v>
@@ -3554,8 +3251,8 @@
       <c r="E81" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F81" s="9"/>
-      <c r="G81" s="11" t="s">
+      <c r="F81" s="6"/>
+      <c r="G81" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H81" s="3">
@@ -3564,17 +3261,17 @@
       <c r="I81" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J81" s="9"/>
+      <c r="J81" s="6"/>
     </row>
     <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="12">
+      <c r="A82" s="9">
         <v>46185</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>266</v>
+        <v>170</v>
       </c>
       <c r="D82" s="2">
         <v>111</v>
@@ -3582,25 +3279,25 @@
       <c r="E82" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F82" s="9"/>
-      <c r="G82" s="11"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="8"/>
       <c r="H82" s="3">
         <v>720000</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J82" s="9"/>
+      <c r="J82" s="6"/>
     </row>
     <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="12">
+      <c r="A83" s="9">
         <v>46209</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>267</v>
+        <v>171</v>
       </c>
       <c r="D83" s="2">
         <v>101</v>
@@ -3608,9 +3305,9 @@
       <c r="E83" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="9"/>
-      <c r="G83" s="11" t="s">
-        <v>272</v>
+      <c r="F83" s="6"/>
+      <c r="G83" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="H83" s="3">
         <v>735000</v>
@@ -3618,17 +3315,17 @@
       <c r="I83" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J83" s="9"/>
+      <c r="J83" s="6"/>
     </row>
     <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="12">
+      <c r="A84" s="9">
         <v>46183</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>268</v>
+        <v>172</v>
       </c>
       <c r="D84" s="2">
         <v>402</v>
@@ -3636,8 +3333,8 @@
       <c r="E84" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F84" s="9"/>
-      <c r="G84" s="11" t="s">
+      <c r="F84" s="6"/>
+      <c r="G84" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H84" s="3">
@@ -3646,17 +3343,17 @@
       <c r="I84" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J84" s="9"/>
+      <c r="J84" s="6"/>
     </row>
     <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="12">
+      <c r="A85" s="9">
         <v>46261</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>269</v>
+        <v>173</v>
       </c>
       <c r="D85" s="2">
         <v>301</v>
@@ -3664,8 +3361,8 @@
       <c r="E85" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F85" s="9"/>
-      <c r="G85" s="11" t="s">
+      <c r="F85" s="6"/>
+      <c r="G85" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H85" s="3">
@@ -3674,17 +3371,17 @@
       <c r="I85" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J85" s="9"/>
+      <c r="J85" s="6"/>
     </row>
     <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="12">
+      <c r="A86" s="9">
         <v>46275</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>270</v>
+        <v>174</v>
       </c>
       <c r="D86" s="2">
         <v>302</v>
@@ -3692,8 +3389,8 @@
       <c r="E86" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="9"/>
-      <c r="G86" s="11" t="s">
+      <c r="F86" s="6"/>
+      <c r="G86" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H86" s="3">
@@ -3702,25 +3399,25 @@
       <c r="I86" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J86" s="9"/>
+      <c r="J86" s="6"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="10">
+      <c r="A87" s="7">
         <v>46266</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="5">
         <v>159.77000000000001</v>
       </c>
       <c r="G87" s="2" t="s">
@@ -3730,26 +3427,26 @@
         <v>2542650</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="10">
+      <c r="A88" s="7">
         <v>46266</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="5">
         <v>47.02</v>
       </c>
       <c r="G88" s="2" t="s">
@@ -3759,26 +3456,26 @@
         <v>1527600</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="10">
+      <c r="A89" s="7">
         <v>46266</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F89" s="5">
         <v>47.02</v>
       </c>
       <c r="G89" s="2" t="s">
@@ -3788,26 +3485,26 @@
         <v>1688400</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="10">
+      <c r="A90" s="7">
         <v>46266</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F90" s="6">
+      <c r="F90" s="5">
         <v>33.17</v>
       </c>
       <c r="G90" s="2" t="s">
@@ -3817,26 +3514,26 @@
         <v>783900</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="10">
+      <c r="A91" s="7">
         <v>46266</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F91" s="5">
         <v>26.78</v>
       </c>
       <c r="G91" s="2" t="s">
@@ -3846,26 +3543,26 @@
         <v>763800</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="10">
+      <c r="A92" s="7">
         <v>46266</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="5">
         <v>30.61</v>
       </c>
       <c r="G92" s="2" t="s">
@@ -3875,26 +3572,26 @@
         <v>824100</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="10">
+      <c r="A93" s="7">
         <v>46266</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F93" s="6">
+      <c r="F93" s="5">
         <v>30.61</v>
       </c>
       <c r="G93" s="2" t="s">
@@ -3904,26 +3601,26 @@
         <v>824100</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="10">
+      <c r="A94" s="7">
         <v>46266</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F94" s="5">
         <v>25.06</v>
       </c>
       <c r="G94" s="2" t="s">
@@ -3933,26 +3630,26 @@
         <v>743700</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="10">
+      <c r="A95" s="7">
         <v>46266</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F95" s="6">
+      <c r="F95" s="5">
         <v>33.24</v>
       </c>
       <c r="G95" s="2" t="s">
@@ -3962,26 +3659,26 @@
         <v>824100</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="10">
+      <c r="A96" s="7">
         <v>46266</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="6">
+      <c r="F96" s="5">
         <v>66.28</v>
       </c>
       <c r="G96" s="2" t="s">
@@ -3991,26 +3688,26 @@
         <v>769362</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="10">
+      <c r="A97" s="7">
         <v>46266</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="5">
         <v>154.47999999999999</v>
       </c>
       <c r="G97" s="2" t="s">
@@ -4020,26 +3717,26 @@
         <v>3097285</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="10">
+      <c r="A98" s="7">
         <v>46266</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F98" s="6">
+      <c r="F98" s="5">
         <v>155.79</v>
       </c>
       <c r="G98" s="2" t="s">
@@ -4049,26 +3746,26 @@
         <v>3123551</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="10">
+      <c r="A99" s="7">
         <v>46266</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F99" s="6">
+      <c r="F99" s="5">
         <v>68.349999999999994</v>
       </c>
       <c r="G99" s="2" t="s">
@@ -4078,26 +3775,26 @@
         <v>793390</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="10">
+      <c r="A100" s="7">
         <v>46266</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F100" s="6">
+      <c r="F100" s="5">
         <v>68.459999999999994</v>
       </c>
       <c r="G100" s="2" t="s">
@@ -4107,26 +3804,26 @@
         <v>794667</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="10">
+      <c r="A101" s="7">
         <v>46266</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F101" s="6">
+      <c r="F101" s="5">
         <v>65.790000000000006</v>
       </c>
       <c r="G101" s="2" t="s">
@@ -4136,26 +3833,26 @@
         <v>763674</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="10">
+      <c r="A102" s="7">
         <v>46266</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F102" s="6">
+      <c r="F102" s="5">
         <v>93.55</v>
       </c>
       <c r="G102" s="2" t="s">
@@ -4165,26 +3862,26 @@
         <v>888468</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="10">
+      <c r="A103" s="7">
         <v>46266</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F103" s="5">
         <v>84.41</v>
       </c>
       <c r="G103" s="2" t="s">
@@ -4194,26 +3891,26 @@
         <v>846200</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="10">
+      <c r="A104" s="7">
         <v>46266</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F104" s="6">
+      <c r="F104" s="5">
         <v>100.14</v>
       </c>
       <c r="G104" s="2" t="s">
@@ -4223,26 +3920,26 @@
         <v>1109564</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="10">
+      <c r="A105" s="7">
         <v>46266</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F105" s="5">
         <v>74.61</v>
       </c>
       <c r="G105" s="2" t="s">
@@ -4252,26 +3949,26 @@
         <v>747956</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="10">
+      <c r="A106" s="7">
         <v>46266</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F106" s="5">
         <v>64.069999999999993</v>
       </c>
       <c r="G106" s="2" t="s">
@@ -4281,26 +3978,26 @@
         <v>743709</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="10">
+      <c r="A107" s="7">
         <v>46266</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F107" s="5">
         <v>155.79</v>
       </c>
       <c r="G107" s="2" t="s">
@@ -4310,26 +4007,26 @@
         <v>3435906</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="10">
+      <c r="A108" s="7">
         <v>46266</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F108" s="5">
         <v>89.06</v>
       </c>
       <c r="G108" s="2" t="s">
@@ -4339,26 +4036,26 @@
         <v>1311028.8799999999</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="10">
+      <c r="A109" s="7">
         <v>46266</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F109" s="5">
         <v>89.08</v>
       </c>
       <c r="G109" s="2" t="s">
@@ -4368,26 +4065,26 @@
         <v>1269022.55</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="10">
+      <c r="A110" s="7">
         <v>46266</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F110" s="5">
         <v>73.87</v>
       </c>
       <c r="G110" s="2" t="s">
@@ -4397,26 +4094,26 @@
         <v>818489</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="10">
+      <c r="A111" s="7">
         <v>46266</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F111" s="6">
+      <c r="F111" s="5">
         <v>124.71</v>
       </c>
       <c r="G111" s="2" t="s">
@@ -4426,26 +4123,26 @@
         <v>2500404</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="10">
+      <c r="A112" s="7">
         <v>46266</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F112" s="5">
         <v>142.78</v>
       </c>
       <c r="G112" s="2" t="s">
@@ -4455,26 +4152,26 @@
         <v>2862703</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" s="10">
+      <c r="A113" s="7">
         <v>46266</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F113" s="5">
         <v>89.06</v>
       </c>
       <c r="G113" s="2" t="s">
@@ -4484,26 +4181,26 @@
         <v>1456699</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" s="10">
+      <c r="A114" s="7">
         <v>46266</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F114" s="5">
         <v>89.08</v>
       </c>
       <c r="G114" s="2" t="s">
@@ -4513,26 +4210,26 @@
         <v>1410025</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A115" s="10">
+      <c r="A115" s="7">
         <v>46266</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F115" s="6">
+      <c r="F115" s="5">
         <v>88.91</v>
       </c>
       <c r="G115" s="2" t="s">
@@ -4542,26 +4239,26 @@
         <v>1360423</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" s="10">
+      <c r="A116" s="7">
         <v>46266</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F116" s="5">
         <v>104.2</v>
       </c>
       <c r="G116" s="2" t="s">
@@ -4571,26 +4268,26 @@
         <v>1539399</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" s="10">
+      <c r="A117" s="7">
         <v>46266</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F117" s="5">
         <v>92.79</v>
       </c>
       <c r="G117" s="2" t="s">
@@ -4600,26 +4297,26 @@
         <v>881250</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A118" s="10">
+      <c r="A118" s="7">
         <v>46266</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>161</v>
+        <v>89</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F118" s="6">
+      <c r="F118" s="5">
         <v>93.1</v>
       </c>
       <c r="G118" s="2" t="s">
@@ -4629,26 +4326,26 @@
         <v>903843</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A119" s="10">
+      <c r="A119" s="7">
         <v>46266</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F119" s="5">
         <v>113.74</v>
       </c>
       <c r="G119" s="2" t="s">
@@ -4658,26 +4355,26 @@
         <v>1200241</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" s="10">
+      <c r="A120" s="7">
         <v>46266</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F120" s="6">
+      <c r="F120" s="5">
         <v>101.16</v>
       </c>
       <c r="G120" s="2" t="s">
@@ -4687,26 +4384,26 @@
         <v>960742</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A121" s="10">
+      <c r="A121" s="7">
         <v>46266</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>164</v>
+        <v>92</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F121" s="5">
         <v>71.86</v>
       </c>
       <c r="G121" s="2" t="s">
@@ -4716,26 +4413,26 @@
         <v>796218</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A122" s="10">
+      <c r="A122" s="7">
         <v>46266</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F122" s="5">
         <v>45.26</v>
       </c>
       <c r="G122" s="2" t="s">
@@ -4745,26 +4442,26 @@
         <v>934650</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A123" s="10">
+      <c r="A123" s="7">
         <v>46266</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F123" s="6">
+      <c r="F123" s="5">
         <v>40.07</v>
       </c>
       <c r="G123" s="2" t="s">
@@ -4774,26 +4471,26 @@
         <v>874350</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A124" s="10">
+      <c r="A124" s="7">
         <v>46266</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F124" s="6">
+      <c r="F124" s="5">
         <v>30.42</v>
       </c>
       <c r="G124" s="2" t="s">
@@ -4803,26 +4500,26 @@
         <v>773850</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A125" s="10">
+      <c r="A125" s="7">
         <v>46266</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F125" s="6">
+      <c r="F125" s="5">
         <v>23.27</v>
       </c>
       <c r="G125" s="2" t="s">
@@ -4832,26 +4529,26 @@
         <v>668325</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A126" s="10">
+      <c r="A126" s="7">
         <v>46266</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F126" s="6">
+      <c r="F126" s="5">
         <v>22.59</v>
       </c>
       <c r="G126" s="2" t="s">
@@ -4861,26 +4558,26 @@
         <v>668325</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" s="10">
+      <c r="A127" s="7">
         <v>46266</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F127" s="6">
+      <c r="F127" s="5">
         <v>26.44</v>
       </c>
       <c r="G127" s="2" t="s">
@@ -4890,11 +4587,11 @@
         <v>733650</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" s="10">
+      <c r="A128" s="7">
         <v>46296</v>
       </c>
       <c r="B128" s="1" t="s">
@@ -4922,11 +4619,11 @@
         <v>6</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>194</v>
+        <v>98</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="10">
+      <c r="A129" s="7">
         <v>46296</v>
       </c>
       <c r="B129" s="1" t="s">
@@ -4954,11 +4651,11 @@
         <v>6</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>194</v>
+        <v>98</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A130" s="10">
+      <c r="A130" s="7">
         <v>46296</v>
       </c>
       <c r="B130" s="1" t="s">
@@ -4986,11 +4683,11 @@
         <v>6</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>194</v>
+        <v>98</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A131" s="10">
+      <c r="A131" s="7">
         <v>46296</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -5018,11 +4715,11 @@
         <v>6</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>196</v>
+        <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A132" s="10">
+      <c r="A132" s="7">
         <v>46296</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -5032,7 +4729,7 @@
         <v>39</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>5</v>
@@ -5050,11 +4747,11 @@
         <v>6</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>194</v>
+        <v>98</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A133" s="10">
+      <c r="A133" s="7">
         <v>46296</v>
       </c>
       <c r="B133" s="1" t="s">
@@ -5082,11 +4779,11 @@
         <v>6</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>196</v>
+        <v>100</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" s="10">
+      <c r="A134" s="7">
         <v>46296</v>
       </c>
       <c r="B134" s="1" t="s">
@@ -5114,11 +4811,11 @@
         <v>6</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>194</v>
+        <v>98</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" s="10">
+      <c r="A135" s="7">
         <v>46296</v>
       </c>
       <c r="B135" s="1" t="s">
@@ -5146,11 +4843,11 @@
         <v>6</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>194</v>
+        <v>98</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" s="10">
+      <c r="A136" s="7">
         <v>46296</v>
       </c>
       <c r="B136" s="1" t="s">
@@ -5178,11 +4875,11 @@
         <v>6</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>194</v>
+        <v>98</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" s="10">
+      <c r="A137" s="7">
         <v>46296</v>
       </c>
       <c r="B137" s="1" t="s">
@@ -5210,11 +4907,11 @@
         <v>6</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>194</v>
+        <v>98</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" s="10">
+      <c r="A138" s="7">
         <v>46296</v>
       </c>
       <c r="B138" s="1" t="s">
@@ -5242,21 +4939,21 @@
         <v>6</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>196</v>
+        <v>100</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" s="10">
+      <c r="A139" s="7">
         <v>46296</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>7</v>
@@ -5274,21 +4971,21 @@
         <v>6</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>195</v>
+        <v>99</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" s="10">
+      <c r="A140" s="7">
         <v>46313</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>197</v>
+        <v>101</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>5</v>
@@ -5306,21 +5003,21 @@
         <v>6</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>195</v>
+        <v>99</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" s="10">
+      <c r="A141" s="7">
         <v>46313</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>198</v>
+        <v>102</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>5</v>
@@ -5338,2031 +5035,2031 @@
         <v>6</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>195</v>
+        <v>99</v>
       </c>
     </row>
     <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="10"/>
+      <c r="A142" s="7"/>
       <c r="H142" s="3"/>
     </row>
     <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="10"/>
+      <c r="A143" s="7"/>
       <c r="H143" s="3"/>
     </row>
     <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="10"/>
+      <c r="A144" s="7"/>
       <c r="H144" s="3"/>
     </row>
     <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="10"/>
+      <c r="A145" s="7"/>
       <c r="H145" s="3"/>
     </row>
     <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="10"/>
+      <c r="A146" s="7"/>
       <c r="H146" s="3"/>
     </row>
     <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="10"/>
+      <c r="A147" s="7"/>
       <c r="H147" s="3"/>
     </row>
     <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="10"/>
+      <c r="A148" s="7"/>
       <c r="H148" s="3"/>
     </row>
     <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="10"/>
+      <c r="A149" s="7"/>
       <c r="H149" s="3"/>
     </row>
     <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="10"/>
+      <c r="A150" s="7"/>
       <c r="H150" s="3"/>
     </row>
     <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="10"/>
+      <c r="A151" s="7"/>
       <c r="H151" s="3"/>
     </row>
     <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="10"/>
+      <c r="A152" s="7"/>
       <c r="H152" s="3"/>
     </row>
     <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="10"/>
+      <c r="A153" s="7"/>
       <c r="H153" s="3"/>
     </row>
     <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="10"/>
+      <c r="A154" s="7"/>
       <c r="H154" s="3"/>
     </row>
     <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="10"/>
+      <c r="A155" s="7"/>
       <c r="H155" s="3"/>
     </row>
     <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="10"/>
+      <c r="A156" s="7"/>
       <c r="H156" s="3"/>
     </row>
     <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="10"/>
+      <c r="A157" s="7"/>
       <c r="H157" s="3"/>
     </row>
     <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="10"/>
+      <c r="A158" s="7"/>
       <c r="H158" s="3"/>
     </row>
     <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="10"/>
+      <c r="A159" s="7"/>
       <c r="H159" s="3"/>
     </row>
     <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="10"/>
+      <c r="A160" s="7"/>
       <c r="H160" s="3"/>
     </row>
     <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="10"/>
+      <c r="A161" s="7"/>
       <c r="H161" s="3"/>
     </row>
     <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="10"/>
+      <c r="A162" s="7"/>
       <c r="H162" s="3"/>
     </row>
     <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="10"/>
+      <c r="A163" s="7"/>
       <c r="H163" s="3"/>
     </row>
     <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="10"/>
+      <c r="A164" s="7"/>
       <c r="H164" s="3"/>
     </row>
     <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="10"/>
+      <c r="A165" s="7"/>
       <c r="H165" s="3"/>
     </row>
     <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="10"/>
+      <c r="A166" s="7"/>
       <c r="H166" s="3"/>
     </row>
     <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="10"/>
+      <c r="A167" s="7"/>
       <c r="H167" s="3"/>
     </row>
     <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="10"/>
+      <c r="A168" s="7"/>
       <c r="H168" s="3"/>
     </row>
     <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="10"/>
+      <c r="A169" s="7"/>
       <c r="H169" s="3"/>
     </row>
     <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="10"/>
+      <c r="A170" s="7"/>
       <c r="H170" s="3"/>
     </row>
     <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="10"/>
+      <c r="A171" s="7"/>
       <c r="H171" s="3"/>
     </row>
     <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="10"/>
+      <c r="A172" s="7"/>
       <c r="H172" s="3"/>
     </row>
     <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="10"/>
+      <c r="A173" s="7"/>
       <c r="H173" s="3"/>
     </row>
     <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="10"/>
+      <c r="A174" s="7"/>
       <c r="H174" s="3"/>
     </row>
     <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="10"/>
+      <c r="A175" s="7"/>
       <c r="H175" s="3"/>
     </row>
     <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="10"/>
+      <c r="A176" s="7"/>
       <c r="H176" s="3"/>
     </row>
     <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="10"/>
+      <c r="A177" s="7"/>
       <c r="H177" s="3"/>
     </row>
     <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="10"/>
+      <c r="A178" s="7"/>
       <c r="H178" s="3"/>
     </row>
     <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="10"/>
+      <c r="A179" s="7"/>
       <c r="H179" s="3"/>
     </row>
     <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="10"/>
+      <c r="A180" s="7"/>
       <c r="H180" s="3"/>
     </row>
     <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="10"/>
+      <c r="A181" s="7"/>
       <c r="H181" s="3"/>
     </row>
     <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="10"/>
+      <c r="A182" s="7"/>
       <c r="H182" s="3"/>
     </row>
     <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="10"/>
+      <c r="A183" s="7"/>
       <c r="H183" s="3"/>
     </row>
     <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="10"/>
+      <c r="A184" s="7"/>
       <c r="H184" s="3"/>
     </row>
     <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="10"/>
+      <c r="A185" s="7"/>
       <c r="H185" s="3"/>
     </row>
     <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="10"/>
+      <c r="A186" s="7"/>
       <c r="H186" s="3"/>
     </row>
     <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="10"/>
+      <c r="A187" s="7"/>
       <c r="H187" s="3"/>
     </row>
     <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="10"/>
+      <c r="A188" s="7"/>
       <c r="H188" s="3"/>
     </row>
     <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="10"/>
+      <c r="A189" s="7"/>
       <c r="H189" s="3"/>
     </row>
     <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="10"/>
+      <c r="A190" s="7"/>
       <c r="H190" s="3"/>
     </row>
     <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="10"/>
+      <c r="A191" s="7"/>
       <c r="H191" s="3"/>
     </row>
     <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="10"/>
+      <c r="A192" s="7"/>
       <c r="H192" s="3"/>
     </row>
     <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="10"/>
+      <c r="A193" s="7"/>
       <c r="H193" s="3"/>
     </row>
     <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="10"/>
+      <c r="A194" s="7"/>
       <c r="H194" s="3"/>
     </row>
     <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="10"/>
+      <c r="A195" s="7"/>
       <c r="H195" s="3"/>
     </row>
     <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="10"/>
+      <c r="A196" s="7"/>
       <c r="H196" s="3"/>
     </row>
     <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="10"/>
+      <c r="A197" s="7"/>
       <c r="H197" s="3"/>
     </row>
     <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="10"/>
+      <c r="A198" s="7"/>
       <c r="H198" s="3"/>
     </row>
     <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="10"/>
+      <c r="A199" s="7"/>
       <c r="H199" s="3"/>
     </row>
     <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="10"/>
+      <c r="A200" s="7"/>
       <c r="H200" s="3"/>
     </row>
     <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="10"/>
+      <c r="A201" s="7"/>
       <c r="H201" s="3"/>
     </row>
     <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="10"/>
+      <c r="A202" s="7"/>
       <c r="H202" s="3"/>
     </row>
     <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="10"/>
+      <c r="A203" s="7"/>
       <c r="H203" s="3"/>
     </row>
     <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="10"/>
+      <c r="A204" s="7"/>
       <c r="H204" s="3"/>
     </row>
     <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="10"/>
+      <c r="A205" s="7"/>
       <c r="H205" s="3"/>
     </row>
     <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="10"/>
+      <c r="A206" s="7"/>
       <c r="H206" s="3"/>
     </row>
     <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="10"/>
+      <c r="A207" s="7"/>
       <c r="H207" s="3"/>
     </row>
     <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="10"/>
+      <c r="A208" s="7"/>
       <c r="H208" s="3"/>
     </row>
     <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="10"/>
+      <c r="A209" s="7"/>
       <c r="H209" s="3"/>
     </row>
     <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="10"/>
+      <c r="A210" s="7"/>
       <c r="H210" s="3"/>
     </row>
     <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="10"/>
+      <c r="A211" s="7"/>
       <c r="H211" s="3"/>
     </row>
     <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="10"/>
+      <c r="A212" s="7"/>
       <c r="H212" s="3"/>
     </row>
     <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="10"/>
+      <c r="A213" s="7"/>
       <c r="H213" s="3"/>
     </row>
     <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="10"/>
+      <c r="A214" s="7"/>
       <c r="H214" s="3"/>
     </row>
     <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="10"/>
+      <c r="A215" s="7"/>
       <c r="H215" s="3"/>
     </row>
     <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="10"/>
+      <c r="A216" s="7"/>
       <c r="H216" s="3"/>
     </row>
     <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="10"/>
+      <c r="A217" s="7"/>
       <c r="H217" s="3"/>
     </row>
     <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="10"/>
+      <c r="A218" s="7"/>
       <c r="H218" s="3"/>
     </row>
     <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="10"/>
+      <c r="A219" s="7"/>
       <c r="H219" s="3"/>
     </row>
     <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="10"/>
+      <c r="A220" s="7"/>
       <c r="H220" s="3"/>
     </row>
     <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="10"/>
+      <c r="A221" s="7"/>
       <c r="H221" s="3"/>
     </row>
     <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="10"/>
+      <c r="A222" s="7"/>
       <c r="H222" s="3"/>
     </row>
     <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="10"/>
+      <c r="A223" s="7"/>
       <c r="H223" s="3"/>
     </row>
     <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="10"/>
+      <c r="A224" s="7"/>
       <c r="H224" s="3"/>
     </row>
     <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="10"/>
+      <c r="A225" s="7"/>
       <c r="H225" s="3"/>
     </row>
     <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="10"/>
+      <c r="A226" s="7"/>
       <c r="H226" s="3"/>
     </row>
     <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="10"/>
+      <c r="A227" s="7"/>
       <c r="H227" s="3"/>
     </row>
     <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="10"/>
+      <c r="A228" s="7"/>
       <c r="H228" s="3"/>
     </row>
     <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="10"/>
+      <c r="A229" s="7"/>
       <c r="H229" s="3"/>
     </row>
     <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="10"/>
+      <c r="A230" s="7"/>
       <c r="H230" s="3"/>
     </row>
     <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="10"/>
+      <c r="A231" s="7"/>
       <c r="H231" s="3"/>
     </row>
     <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="10"/>
+      <c r="A232" s="7"/>
       <c r="H232" s="3"/>
     </row>
     <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="10"/>
+      <c r="A233" s="7"/>
       <c r="H233" s="3"/>
     </row>
     <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="10"/>
+      <c r="A234" s="7"/>
       <c r="H234" s="3"/>
     </row>
     <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="10"/>
+      <c r="A235" s="7"/>
       <c r="H235" s="3"/>
     </row>
     <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="10"/>
+      <c r="A236" s="7"/>
       <c r="H236" s="3"/>
     </row>
     <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="10"/>
+      <c r="A237" s="7"/>
       <c r="H237" s="3"/>
     </row>
     <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="10"/>
+      <c r="A238" s="7"/>
       <c r="H238" s="3"/>
     </row>
     <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="10"/>
+      <c r="A239" s="7"/>
       <c r="H239" s="3"/>
     </row>
     <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="10"/>
+      <c r="A240" s="7"/>
       <c r="H240" s="3"/>
     </row>
     <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="10"/>
+      <c r="A241" s="7"/>
       <c r="H241" s="3"/>
     </row>
     <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="10"/>
+      <c r="A242" s="7"/>
       <c r="H242" s="3"/>
     </row>
     <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="10"/>
+      <c r="A243" s="7"/>
       <c r="H243" s="3"/>
     </row>
     <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="10"/>
+      <c r="A244" s="7"/>
       <c r="H244" s="3"/>
     </row>
     <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="10"/>
+      <c r="A245" s="7"/>
       <c r="H245" s="3"/>
     </row>
     <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="10"/>
+      <c r="A246" s="7"/>
       <c r="H246" s="3"/>
     </row>
     <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="10"/>
+      <c r="A247" s="7"/>
       <c r="H247" s="3"/>
     </row>
     <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="10"/>
+      <c r="A248" s="7"/>
       <c r="H248" s="3"/>
     </row>
     <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="10"/>
+      <c r="A249" s="7"/>
       <c r="H249" s="3"/>
     </row>
     <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="10"/>
+      <c r="A250" s="7"/>
       <c r="H250" s="3"/>
     </row>
     <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="10"/>
+      <c r="A251" s="7"/>
       <c r="H251" s="3"/>
     </row>
     <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="10"/>
+      <c r="A252" s="7"/>
       <c r="H252" s="3"/>
     </row>
     <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="10"/>
+      <c r="A253" s="7"/>
       <c r="H253" s="3"/>
     </row>
     <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="10"/>
+      <c r="A254" s="7"/>
       <c r="H254" s="3"/>
     </row>
     <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A255" s="10"/>
+      <c r="A255" s="7"/>
       <c r="H255" s="3"/>
     </row>
     <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A256" s="10"/>
+      <c r="A256" s="7"/>
       <c r="H256" s="3"/>
     </row>
     <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A257" s="10"/>
+      <c r="A257" s="7"/>
       <c r="H257" s="3"/>
     </row>
     <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A258" s="10"/>
+      <c r="A258" s="7"/>
       <c r="H258" s="3"/>
     </row>
     <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="10"/>
+      <c r="A259" s="7"/>
       <c r="H259" s="3"/>
     </row>
     <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A260" s="10"/>
+      <c r="A260" s="7"/>
       <c r="H260" s="3"/>
     </row>
     <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A261" s="10"/>
+      <c r="A261" s="7"/>
       <c r="H261" s="3"/>
     </row>
     <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A262" s="10"/>
+      <c r="A262" s="7"/>
       <c r="H262" s="3"/>
     </row>
     <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A263" s="10"/>
+      <c r="A263" s="7"/>
       <c r="H263" s="3"/>
     </row>
     <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A264" s="10"/>
+      <c r="A264" s="7"/>
       <c r="H264" s="3"/>
     </row>
     <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A265" s="10"/>
+      <c r="A265" s="7"/>
       <c r="H265" s="3"/>
     </row>
     <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="10"/>
+      <c r="A266" s="7"/>
       <c r="H266" s="3"/>
     </row>
     <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A267" s="10"/>
+      <c r="A267" s="7"/>
       <c r="H267" s="3"/>
     </row>
     <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A268" s="10"/>
+      <c r="A268" s="7"/>
       <c r="H268" s="3"/>
     </row>
     <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A269" s="10"/>
+      <c r="A269" s="7"/>
       <c r="H269" s="3"/>
     </row>
     <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A270" s="10"/>
+      <c r="A270" s="7"/>
       <c r="H270" s="3"/>
     </row>
     <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A271" s="10"/>
+      <c r="A271" s="7"/>
       <c r="H271" s="3"/>
     </row>
     <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A272" s="10"/>
+      <c r="A272" s="7"/>
       <c r="H272" s="3"/>
     </row>
     <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="10"/>
+      <c r="A273" s="7"/>
       <c r="H273" s="3"/>
     </row>
     <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A274" s="10"/>
+      <c r="A274" s="7"/>
       <c r="H274" s="3"/>
     </row>
     <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A275" s="10"/>
+      <c r="A275" s="7"/>
       <c r="H275" s="3"/>
     </row>
     <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A276" s="10"/>
+      <c r="A276" s="7"/>
       <c r="H276" s="3"/>
     </row>
     <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A277" s="10"/>
+      <c r="A277" s="7"/>
       <c r="H277" s="3"/>
     </row>
     <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A278" s="10"/>
+      <c r="A278" s="7"/>
       <c r="H278" s="3"/>
     </row>
     <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A279" s="10"/>
+      <c r="A279" s="7"/>
       <c r="H279" s="3"/>
     </row>
     <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A280" s="10"/>
+      <c r="A280" s="7"/>
       <c r="H280" s="3"/>
     </row>
     <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A281" s="10"/>
+      <c r="A281" s="7"/>
       <c r="H281" s="3"/>
     </row>
     <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A282" s="10"/>
+      <c r="A282" s="7"/>
       <c r="H282" s="3"/>
     </row>
     <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A283" s="10"/>
+      <c r="A283" s="7"/>
       <c r="H283" s="3"/>
     </row>
     <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A284" s="10"/>
+      <c r="A284" s="7"/>
       <c r="H284" s="3"/>
     </row>
     <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A285" s="10"/>
+      <c r="A285" s="7"/>
       <c r="H285" s="3"/>
     </row>
     <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A286" s="10"/>
+      <c r="A286" s="7"/>
       <c r="H286" s="3"/>
     </row>
     <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="10"/>
+      <c r="A287" s="7"/>
       <c r="H287" s="3"/>
     </row>
     <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="10"/>
+      <c r="A288" s="7"/>
       <c r="H288" s="3"/>
     </row>
     <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A289" s="10"/>
+      <c r="A289" s="7"/>
       <c r="H289" s="3"/>
     </row>
     <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A290" s="10"/>
+      <c r="A290" s="7"/>
       <c r="H290" s="3"/>
     </row>
     <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A291" s="10"/>
+      <c r="A291" s="7"/>
       <c r="H291" s="3"/>
     </row>
     <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="10"/>
+      <c r="A292" s="7"/>
       <c r="H292" s="3"/>
     </row>
     <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A293" s="10"/>
+      <c r="A293" s="7"/>
       <c r="H293" s="3"/>
     </row>
     <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A294" s="10"/>
+      <c r="A294" s="7"/>
       <c r="H294" s="3"/>
     </row>
     <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A295" s="10"/>
+      <c r="A295" s="7"/>
       <c r="H295" s="3"/>
     </row>
     <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A296" s="10"/>
+      <c r="A296" s="7"/>
       <c r="H296" s="3"/>
     </row>
     <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A297" s="10"/>
+      <c r="A297" s="7"/>
       <c r="H297" s="3"/>
     </row>
     <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A298" s="10"/>
+      <c r="A298" s="7"/>
       <c r="H298" s="3"/>
     </row>
     <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A299" s="10"/>
+      <c r="A299" s="7"/>
       <c r="H299" s="3"/>
     </row>
     <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A300" s="10"/>
+      <c r="A300" s="7"/>
       <c r="H300" s="3"/>
     </row>
     <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A301" s="10"/>
+      <c r="A301" s="7"/>
       <c r="H301" s="3"/>
     </row>
     <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A302" s="10"/>
+      <c r="A302" s="7"/>
       <c r="H302" s="3"/>
     </row>
     <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A303" s="10"/>
+      <c r="A303" s="7"/>
       <c r="H303" s="3"/>
     </row>
     <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A304" s="10"/>
+      <c r="A304" s="7"/>
       <c r="H304" s="3"/>
     </row>
     <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A305" s="10"/>
+      <c r="A305" s="7"/>
       <c r="H305" s="3"/>
     </row>
     <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A306" s="10"/>
+      <c r="A306" s="7"/>
       <c r="H306" s="3"/>
     </row>
     <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A307" s="10"/>
+      <c r="A307" s="7"/>
       <c r="H307" s="3"/>
     </row>
     <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A308" s="10"/>
+      <c r="A308" s="7"/>
       <c r="H308" s="3"/>
     </row>
     <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A309" s="10"/>
+      <c r="A309" s="7"/>
       <c r="H309" s="3"/>
     </row>
     <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A310" s="10"/>
+      <c r="A310" s="7"/>
       <c r="H310" s="3"/>
     </row>
     <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="10"/>
+      <c r="A311" s="7"/>
       <c r="H311" s="3"/>
     </row>
     <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A312" s="10"/>
+      <c r="A312" s="7"/>
       <c r="H312" s="3"/>
     </row>
     <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A313" s="10"/>
+      <c r="A313" s="7"/>
       <c r="H313" s="3"/>
     </row>
     <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A314" s="10"/>
+      <c r="A314" s="7"/>
       <c r="H314" s="3"/>
     </row>
     <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A315" s="10"/>
+      <c r="A315" s="7"/>
       <c r="H315" s="3"/>
     </row>
     <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A316" s="10"/>
+      <c r="A316" s="7"/>
       <c r="H316" s="3"/>
     </row>
     <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A317" s="10"/>
+      <c r="A317" s="7"/>
       <c r="H317" s="3"/>
     </row>
     <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A318" s="10"/>
+      <c r="A318" s="7"/>
       <c r="H318" s="3"/>
     </row>
     <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A319" s="10"/>
+      <c r="A319" s="7"/>
       <c r="H319" s="3"/>
     </row>
     <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A320" s="10"/>
+      <c r="A320" s="7"/>
       <c r="H320" s="3"/>
     </row>
     <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A321" s="10"/>
+      <c r="A321" s="7"/>
       <c r="H321" s="3"/>
     </row>
     <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A322" s="10"/>
+      <c r="A322" s="7"/>
       <c r="H322" s="3"/>
     </row>
     <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A323" s="10"/>
+      <c r="A323" s="7"/>
       <c r="H323" s="3"/>
     </row>
     <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="10"/>
+      <c r="A324" s="7"/>
       <c r="H324" s="3"/>
     </row>
     <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="10"/>
+      <c r="A325" s="7"/>
       <c r="H325" s="3"/>
     </row>
     <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A326" s="10"/>
+      <c r="A326" s="7"/>
       <c r="H326" s="3"/>
     </row>
     <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A327" s="10"/>
+      <c r="A327" s="7"/>
       <c r="H327" s="3"/>
     </row>
     <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A328" s="10"/>
+      <c r="A328" s="7"/>
       <c r="H328" s="3"/>
     </row>
     <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A329" s="10"/>
+      <c r="A329" s="7"/>
       <c r="H329" s="3"/>
     </row>
     <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A330" s="10"/>
+      <c r="A330" s="7"/>
       <c r="H330" s="3"/>
     </row>
     <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A331" s="10"/>
+      <c r="A331" s="7"/>
       <c r="H331" s="3"/>
     </row>
     <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A332" s="10"/>
+      <c r="A332" s="7"/>
       <c r="H332" s="3"/>
     </row>
     <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A333" s="10"/>
+      <c r="A333" s="7"/>
       <c r="H333" s="3"/>
     </row>
     <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A334" s="10"/>
+      <c r="A334" s="7"/>
       <c r="H334" s="3"/>
     </row>
     <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A335" s="10"/>
+      <c r="A335" s="7"/>
       <c r="H335" s="3"/>
     </row>
     <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A336" s="10"/>
+      <c r="A336" s="7"/>
       <c r="H336" s="3"/>
     </row>
     <row r="337" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A337" s="10"/>
+      <c r="A337" s="7"/>
       <c r="H337" s="3"/>
     </row>
     <row r="338" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A338" s="10"/>
+      <c r="A338" s="7"/>
       <c r="H338" s="3"/>
     </row>
     <row r="339" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A339" s="10"/>
+      <c r="A339" s="7"/>
       <c r="H339" s="3"/>
     </row>
     <row r="340" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A340" s="10"/>
+      <c r="A340" s="7"/>
       <c r="H340" s="3"/>
     </row>
     <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A341" s="10"/>
+      <c r="A341" s="7"/>
       <c r="H341" s="3"/>
     </row>
     <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A342" s="10"/>
+      <c r="A342" s="7"/>
       <c r="H342" s="3"/>
     </row>
     <row r="343" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A343" s="10"/>
+      <c r="A343" s="7"/>
       <c r="H343" s="3"/>
     </row>
     <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A344" s="10"/>
+      <c r="A344" s="7"/>
       <c r="H344" s="3"/>
     </row>
     <row r="345" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A345" s="10"/>
+      <c r="A345" s="7"/>
       <c r="H345" s="3"/>
     </row>
     <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A346" s="10"/>
+      <c r="A346" s="7"/>
       <c r="H346" s="3"/>
     </row>
     <row r="347" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A347" s="10"/>
+      <c r="A347" s="7"/>
       <c r="H347" s="3"/>
     </row>
     <row r="348" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A348" s="10"/>
+      <c r="A348" s="7"/>
       <c r="H348" s="3"/>
     </row>
     <row r="349" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A349" s="10"/>
+      <c r="A349" s="7"/>
       <c r="H349" s="3"/>
     </row>
     <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A350" s="10"/>
+      <c r="A350" s="7"/>
       <c r="H350" s="3"/>
     </row>
     <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A351" s="10"/>
+      <c r="A351" s="7"/>
       <c r="H351" s="3"/>
     </row>
     <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A352" s="10"/>
+      <c r="A352" s="7"/>
       <c r="H352" s="3"/>
     </row>
     <row r="353" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A353" s="10"/>
+      <c r="A353" s="7"/>
       <c r="H353" s="3"/>
     </row>
     <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="10"/>
+      <c r="A354" s="7"/>
       <c r="H354" s="3"/>
     </row>
     <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="10"/>
+      <c r="A355" s="7"/>
       <c r="H355" s="3"/>
     </row>
     <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="10"/>
+      <c r="A356" s="7"/>
       <c r="H356" s="3"/>
     </row>
     <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A357" s="10"/>
+      <c r="A357" s="7"/>
       <c r="H357" s="3"/>
     </row>
     <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A358" s="10"/>
+      <c r="A358" s="7"/>
       <c r="H358" s="3"/>
     </row>
     <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A359" s="10"/>
+      <c r="A359" s="7"/>
       <c r="H359" s="3"/>
     </row>
     <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A360" s="10"/>
+      <c r="A360" s="7"/>
       <c r="H360" s="3"/>
     </row>
     <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A361" s="10"/>
+      <c r="A361" s="7"/>
       <c r="H361" s="3"/>
     </row>
     <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A362" s="10"/>
+      <c r="A362" s="7"/>
       <c r="H362" s="3"/>
     </row>
     <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A363" s="10"/>
+      <c r="A363" s="7"/>
       <c r="H363" s="3"/>
     </row>
     <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A364" s="10"/>
+      <c r="A364" s="7"/>
       <c r="H364" s="3"/>
     </row>
     <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A365" s="10"/>
+      <c r="A365" s="7"/>
       <c r="H365" s="3"/>
     </row>
     <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A366" s="10"/>
+      <c r="A366" s="7"/>
       <c r="H366" s="3"/>
     </row>
     <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A367" s="10"/>
+      <c r="A367" s="7"/>
       <c r="H367" s="3"/>
     </row>
     <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A368" s="10"/>
+      <c r="A368" s="7"/>
       <c r="H368" s="3"/>
     </row>
     <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A369" s="10"/>
+      <c r="A369" s="7"/>
       <c r="H369" s="3"/>
     </row>
     <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A370" s="10"/>
+      <c r="A370" s="7"/>
       <c r="H370" s="3"/>
     </row>
     <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A371" s="10"/>
+      <c r="A371" s="7"/>
       <c r="H371" s="3"/>
     </row>
     <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A372" s="10"/>
+      <c r="A372" s="7"/>
       <c r="H372" s="3"/>
     </row>
     <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A373" s="10"/>
+      <c r="A373" s="7"/>
       <c r="H373" s="3"/>
     </row>
     <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A374" s="10"/>
+      <c r="A374" s="7"/>
       <c r="H374" s="3"/>
     </row>
     <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A375" s="10"/>
+      <c r="A375" s="7"/>
       <c r="H375" s="3"/>
     </row>
     <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A376" s="10"/>
+      <c r="A376" s="7"/>
       <c r="H376" s="3"/>
     </row>
     <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A377" s="10"/>
+      <c r="A377" s="7"/>
       <c r="H377" s="3"/>
     </row>
     <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A378" s="10"/>
+      <c r="A378" s="7"/>
       <c r="H378" s="3"/>
     </row>
     <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A379" s="10"/>
+      <c r="A379" s="7"/>
       <c r="H379" s="3"/>
     </row>
     <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A380" s="10"/>
+      <c r="A380" s="7"/>
       <c r="H380" s="3"/>
     </row>
     <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="10"/>
+      <c r="A381" s="7"/>
       <c r="H381" s="3"/>
     </row>
     <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="10"/>
+      <c r="A382" s="7"/>
       <c r="H382" s="3"/>
     </row>
     <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A383" s="10"/>
+      <c r="A383" s="7"/>
       <c r="H383" s="3"/>
     </row>
     <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A384" s="10"/>
+      <c r="A384" s="7"/>
       <c r="H384" s="3"/>
     </row>
     <row r="385" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A385" s="10"/>
+      <c r="A385" s="7"/>
       <c r="H385" s="3"/>
     </row>
     <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A386" s="10"/>
+      <c r="A386" s="7"/>
       <c r="H386" s="3"/>
     </row>
     <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A387" s="10"/>
+      <c r="A387" s="7"/>
       <c r="H387" s="3"/>
     </row>
     <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A388" s="10"/>
+      <c r="A388" s="7"/>
       <c r="H388" s="3"/>
     </row>
     <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A389" s="10"/>
+      <c r="A389" s="7"/>
       <c r="H389" s="3"/>
     </row>
     <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A390" s="10"/>
+      <c r="A390" s="7"/>
       <c r="H390" s="3"/>
     </row>
     <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A391" s="10"/>
+      <c r="A391" s="7"/>
       <c r="H391" s="3"/>
     </row>
     <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A392" s="10"/>
+      <c r="A392" s="7"/>
       <c r="H392" s="3"/>
     </row>
     <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A393" s="10"/>
+      <c r="A393" s="7"/>
       <c r="H393" s="3"/>
     </row>
     <row r="394" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A394" s="10"/>
+      <c r="A394" s="7"/>
       <c r="H394" s="3"/>
     </row>
     <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A395" s="10"/>
+      <c r="A395" s="7"/>
       <c r="H395" s="3"/>
     </row>
     <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A396" s="10"/>
+      <c r="A396" s="7"/>
       <c r="H396" s="3"/>
     </row>
     <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A397" s="10"/>
+      <c r="A397" s="7"/>
       <c r="H397" s="3"/>
     </row>
     <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A398" s="10"/>
+      <c r="A398" s="7"/>
       <c r="H398" s="3"/>
     </row>
     <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A399" s="10"/>
+      <c r="A399" s="7"/>
       <c r="H399" s="3"/>
     </row>
     <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A400" s="10"/>
+      <c r="A400" s="7"/>
       <c r="H400" s="3"/>
     </row>
     <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A401" s="10"/>
+      <c r="A401" s="7"/>
       <c r="H401" s="3"/>
     </row>
     <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A402" s="10"/>
+      <c r="A402" s="7"/>
       <c r="H402" s="3"/>
     </row>
     <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A403" s="10"/>
+      <c r="A403" s="7"/>
       <c r="H403" s="3"/>
     </row>
     <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A404" s="10"/>
+      <c r="A404" s="7"/>
       <c r="H404" s="3"/>
     </row>
     <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A405" s="10"/>
+      <c r="A405" s="7"/>
       <c r="H405" s="3"/>
     </row>
     <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A406" s="10"/>
+      <c r="A406" s="7"/>
       <c r="H406" s="3"/>
     </row>
     <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A407" s="10"/>
+      <c r="A407" s="7"/>
       <c r="H407" s="3"/>
     </row>
     <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A408" s="10"/>
+      <c r="A408" s="7"/>
       <c r="H408" s="3"/>
     </row>
     <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A409" s="10"/>
+      <c r="A409" s="7"/>
       <c r="H409" s="3"/>
     </row>
     <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A410" s="10"/>
+      <c r="A410" s="7"/>
       <c r="H410" s="3"/>
     </row>
     <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A411" s="10"/>
+      <c r="A411" s="7"/>
       <c r="H411" s="3"/>
     </row>
     <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A412" s="10"/>
+      <c r="A412" s="7"/>
       <c r="H412" s="3"/>
     </row>
     <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A413" s="10"/>
+      <c r="A413" s="7"/>
       <c r="H413" s="3"/>
     </row>
     <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A414" s="10"/>
+      <c r="A414" s="7"/>
       <c r="H414" s="3"/>
     </row>
     <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A415" s="10"/>
+      <c r="A415" s="7"/>
       <c r="H415" s="3"/>
     </row>
     <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A416" s="10"/>
+      <c r="A416" s="7"/>
       <c r="H416" s="3"/>
     </row>
     <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A417" s="10"/>
+      <c r="A417" s="7"/>
       <c r="H417" s="3"/>
     </row>
     <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A418" s="10"/>
+      <c r="A418" s="7"/>
       <c r="H418" s="3"/>
     </row>
     <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A419" s="10"/>
+      <c r="A419" s="7"/>
       <c r="H419" s="3"/>
     </row>
     <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A420" s="10"/>
+      <c r="A420" s="7"/>
       <c r="H420" s="3"/>
     </row>
     <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A421" s="10"/>
+      <c r="A421" s="7"/>
       <c r="H421" s="3"/>
     </row>
     <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="10"/>
+      <c r="A422" s="7"/>
       <c r="H422" s="3"/>
     </row>
     <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A423" s="10"/>
+      <c r="A423" s="7"/>
       <c r="H423" s="3"/>
     </row>
     <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A424" s="10"/>
+      <c r="A424" s="7"/>
       <c r="H424" s="3"/>
     </row>
     <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A425" s="10"/>
+      <c r="A425" s="7"/>
       <c r="H425" s="3"/>
     </row>
     <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A426" s="10"/>
+      <c r="A426" s="7"/>
       <c r="H426" s="3"/>
     </row>
     <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A427" s="10"/>
+      <c r="A427" s="7"/>
       <c r="H427" s="3"/>
     </row>
     <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A428" s="10"/>
+      <c r="A428" s="7"/>
       <c r="H428" s="3"/>
     </row>
     <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A429" s="10"/>
+      <c r="A429" s="7"/>
       <c r="H429" s="3"/>
     </row>
     <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A430" s="10"/>
+      <c r="A430" s="7"/>
       <c r="H430" s="3"/>
     </row>
     <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A431" s="10"/>
+      <c r="A431" s="7"/>
       <c r="H431" s="3"/>
     </row>
     <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A432" s="10"/>
+      <c r="A432" s="7"/>
       <c r="H432" s="3"/>
     </row>
     <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A433" s="10"/>
+      <c r="A433" s="7"/>
       <c r="H433" s="3"/>
     </row>
     <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A434" s="10"/>
+      <c r="A434" s="7"/>
       <c r="H434" s="3"/>
     </row>
     <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A435" s="10"/>
+      <c r="A435" s="7"/>
       <c r="H435" s="3"/>
     </row>
     <row r="436" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A436" s="10"/>
+      <c r="A436" s="7"/>
       <c r="H436" s="3"/>
     </row>
     <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A437" s="10"/>
+      <c r="A437" s="7"/>
       <c r="H437" s="3"/>
     </row>
     <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A438" s="10"/>
+      <c r="A438" s="7"/>
       <c r="H438" s="3"/>
     </row>
     <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A439" s="10"/>
+      <c r="A439" s="7"/>
       <c r="H439" s="3"/>
     </row>
     <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A440" s="10"/>
+      <c r="A440" s="7"/>
       <c r="H440" s="3"/>
     </row>
     <row r="441" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A441" s="10"/>
+      <c r="A441" s="7"/>
       <c r="H441" s="3"/>
     </row>
     <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A442" s="10"/>
+      <c r="A442" s="7"/>
       <c r="H442" s="3"/>
     </row>
     <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A443" s="10"/>
+      <c r="A443" s="7"/>
       <c r="H443" s="3"/>
     </row>
     <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A444" s="10"/>
+      <c r="A444" s="7"/>
       <c r="H444" s="3"/>
     </row>
     <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A445" s="10"/>
+      <c r="A445" s="7"/>
       <c r="H445" s="3"/>
     </row>
     <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A446" s="10"/>
+      <c r="A446" s="7"/>
       <c r="H446" s="3"/>
     </row>
     <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A447" s="10"/>
+      <c r="A447" s="7"/>
       <c r="H447" s="3"/>
     </row>
     <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A448" s="10"/>
+      <c r="A448" s="7"/>
       <c r="H448" s="3"/>
     </row>
     <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A449" s="10"/>
+      <c r="A449" s="7"/>
       <c r="H449" s="3"/>
     </row>
     <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A450" s="10"/>
+      <c r="A450" s="7"/>
       <c r="H450" s="3"/>
     </row>
     <row r="451" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A451" s="10"/>
+      <c r="A451" s="7"/>
       <c r="H451" s="3"/>
     </row>
     <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A452" s="10"/>
+      <c r="A452" s="7"/>
       <c r="H452" s="3"/>
     </row>
     <row r="453" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A453" s="10"/>
+      <c r="A453" s="7"/>
       <c r="H453" s="3"/>
     </row>
     <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A454" s="10"/>
+      <c r="A454" s="7"/>
       <c r="H454" s="3"/>
     </row>
     <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A455" s="10"/>
+      <c r="A455" s="7"/>
       <c r="H455" s="3"/>
     </row>
     <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A456" s="10"/>
+      <c r="A456" s="7"/>
       <c r="H456" s="3"/>
     </row>
     <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A457" s="10"/>
+      <c r="A457" s="7"/>
       <c r="H457" s="3"/>
     </row>
     <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A458" s="10"/>
+      <c r="A458" s="7"/>
       <c r="H458" s="3"/>
     </row>
     <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A459" s="10"/>
+      <c r="A459" s="7"/>
       <c r="H459" s="3"/>
     </row>
     <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="10"/>
+      <c r="A460" s="7"/>
       <c r="H460" s="3"/>
     </row>
     <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="10"/>
+      <c r="A461" s="7"/>
       <c r="H461" s="3"/>
     </row>
     <row r="462" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A462" s="10"/>
+      <c r="A462" s="7"/>
       <c r="H462" s="3"/>
     </row>
     <row r="463" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A463" s="10"/>
+      <c r="A463" s="7"/>
       <c r="H463" s="3"/>
     </row>
     <row r="464" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A464" s="10"/>
+      <c r="A464" s="7"/>
       <c r="H464" s="3"/>
     </row>
     <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A465" s="10"/>
+      <c r="A465" s="7"/>
       <c r="H465" s="3"/>
     </row>
     <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A466" s="10"/>
+      <c r="A466" s="7"/>
       <c r="H466" s="3"/>
     </row>
     <row r="467" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A467" s="10"/>
+      <c r="A467" s="7"/>
       <c r="H467" s="3"/>
     </row>
     <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A468" s="10"/>
+      <c r="A468" s="7"/>
       <c r="H468" s="3"/>
     </row>
     <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A469" s="10"/>
+      <c r="A469" s="7"/>
       <c r="H469" s="3"/>
     </row>
     <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A470" s="10"/>
+      <c r="A470" s="7"/>
       <c r="H470" s="3"/>
     </row>
     <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A471" s="10"/>
+      <c r="A471" s="7"/>
       <c r="H471" s="3"/>
     </row>
     <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A472" s="10"/>
+      <c r="A472" s="7"/>
       <c r="H472" s="3"/>
     </row>
     <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A473" s="10"/>
+      <c r="A473" s="7"/>
       <c r="H473" s="3"/>
     </row>
     <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A474" s="10"/>
+      <c r="A474" s="7"/>
       <c r="H474" s="3"/>
     </row>
     <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A475" s="10"/>
+      <c r="A475" s="7"/>
       <c r="H475" s="3"/>
     </row>
     <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A476" s="10"/>
+      <c r="A476" s="7"/>
       <c r="H476" s="3"/>
     </row>
     <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A477" s="10"/>
+      <c r="A477" s="7"/>
       <c r="H477" s="3"/>
     </row>
     <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A478" s="10"/>
+      <c r="A478" s="7"/>
       <c r="H478" s="3"/>
     </row>
     <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="10"/>
+      <c r="A479" s="7"/>
       <c r="H479" s="3"/>
     </row>
     <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="10"/>
+      <c r="A480" s="7"/>
       <c r="H480" s="3"/>
     </row>
     <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A481" s="10"/>
+      <c r="A481" s="7"/>
       <c r="H481" s="3"/>
     </row>
     <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A482" s="10"/>
+      <c r="A482" s="7"/>
       <c r="H482" s="3"/>
     </row>
     <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A483" s="10"/>
+      <c r="A483" s="7"/>
       <c r="H483" s="3"/>
     </row>
     <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A484" s="10"/>
+      <c r="A484" s="7"/>
       <c r="H484" s="3"/>
     </row>
     <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A485" s="10"/>
+      <c r="A485" s="7"/>
       <c r="H485" s="3"/>
     </row>
     <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A486" s="10"/>
+      <c r="A486" s="7"/>
       <c r="H486" s="3"/>
     </row>
     <row r="487" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A487" s="10"/>
+      <c r="A487" s="7"/>
       <c r="H487" s="3"/>
     </row>
     <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A488" s="10"/>
+      <c r="A488" s="7"/>
       <c r="H488" s="3"/>
     </row>
     <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A489" s="10"/>
+      <c r="A489" s="7"/>
       <c r="H489" s="3"/>
     </row>
     <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A490" s="10"/>
+      <c r="A490" s="7"/>
       <c r="H490" s="3"/>
     </row>
     <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A491" s="10"/>
+      <c r="A491" s="7"/>
       <c r="H491" s="3"/>
     </row>
     <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A492" s="10"/>
+      <c r="A492" s="7"/>
       <c r="H492" s="3"/>
     </row>
     <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A493" s="10"/>
+      <c r="A493" s="7"/>
       <c r="H493" s="3"/>
     </row>
     <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A494" s="10"/>
+      <c r="A494" s="7"/>
       <c r="H494" s="3"/>
     </row>
     <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A495" s="10"/>
+      <c r="A495" s="7"/>
       <c r="H495" s="3"/>
     </row>
     <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A496" s="10"/>
+      <c r="A496" s="7"/>
       <c r="H496" s="3"/>
     </row>
     <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A497" s="10"/>
+      <c r="A497" s="7"/>
       <c r="H497" s="3"/>
     </row>
     <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A498" s="10"/>
+      <c r="A498" s="7"/>
       <c r="H498" s="3"/>
     </row>
     <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A499" s="10"/>
+      <c r="A499" s="7"/>
       <c r="H499" s="3"/>
     </row>
     <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A500" s="10"/>
+      <c r="A500" s="7"/>
       <c r="H500" s="3"/>
     </row>
     <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A501" s="10"/>
+      <c r="A501" s="7"/>
       <c r="H501" s="3"/>
     </row>
     <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A502" s="10"/>
+      <c r="A502" s="7"/>
       <c r="H502" s="3"/>
     </row>
     <row r="503" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A503" s="10"/>
+      <c r="A503" s="7"/>
       <c r="H503" s="3"/>
     </row>
     <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A504" s="10"/>
+      <c r="A504" s="7"/>
       <c r="H504" s="3"/>
     </row>
     <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A505" s="10"/>
+      <c r="A505" s="7"/>
       <c r="H505" s="3"/>
     </row>
     <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="10"/>
+      <c r="A506" s="7"/>
       <c r="H506" s="3"/>
     </row>
     <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="10"/>
+      <c r="A507" s="7"/>
       <c r="H507" s="3"/>
     </row>
     <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A508" s="10"/>
+      <c r="A508" s="7"/>
       <c r="H508" s="3"/>
     </row>
     <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A509" s="10"/>
+      <c r="A509" s="7"/>
       <c r="H509" s="3"/>
     </row>
     <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A510" s="10"/>
+      <c r="A510" s="7"/>
       <c r="H510" s="3"/>
     </row>
     <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A511" s="10"/>
+      <c r="A511" s="7"/>
       <c r="H511" s="3"/>
     </row>
     <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A512" s="10"/>
+      <c r="A512" s="7"/>
       <c r="H512" s="3"/>
     </row>
     <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A513" s="10"/>
+      <c r="A513" s="7"/>
       <c r="H513" s="3"/>
     </row>
     <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A514" s="10"/>
+      <c r="A514" s="7"/>
       <c r="H514" s="3"/>
     </row>
     <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A515" s="10"/>
+      <c r="A515" s="7"/>
       <c r="H515" s="3"/>
     </row>
     <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A516" s="10"/>
+      <c r="A516" s="7"/>
       <c r="H516" s="3"/>
     </row>
     <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A517" s="10"/>
+      <c r="A517" s="7"/>
       <c r="H517" s="3"/>
     </row>
     <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A518" s="10"/>
+      <c r="A518" s="7"/>
       <c r="H518" s="3"/>
     </row>
     <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A519" s="10"/>
+      <c r="A519" s="7"/>
       <c r="H519" s="3"/>
     </row>
     <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A520" s="10"/>
+      <c r="A520" s="7"/>
       <c r="H520" s="3"/>
     </row>
     <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A521" s="10"/>
+      <c r="A521" s="7"/>
       <c r="H521" s="3"/>
     </row>
     <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A522" s="10"/>
+      <c r="A522" s="7"/>
       <c r="H522" s="3"/>
     </row>
     <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A523" s="10"/>
+      <c r="A523" s="7"/>
       <c r="H523" s="3"/>
     </row>
     <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A524" s="10"/>
+      <c r="A524" s="7"/>
       <c r="H524" s="3"/>
     </row>
     <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A525" s="10"/>
+      <c r="A525" s="7"/>
       <c r="H525" s="3"/>
     </row>
     <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A526" s="10"/>
+      <c r="A526" s="7"/>
       <c r="H526" s="3"/>
     </row>
     <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A527" s="10"/>
+      <c r="A527" s="7"/>
       <c r="H527" s="3"/>
     </row>
     <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A528" s="10"/>
+      <c r="A528" s="7"/>
       <c r="H528" s="3"/>
     </row>
     <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A529" s="10"/>
+      <c r="A529" s="7"/>
       <c r="H529" s="3"/>
     </row>
     <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A530" s="10"/>
+      <c r="A530" s="7"/>
       <c r="H530" s="3"/>
     </row>
     <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A531" s="10"/>
+      <c r="A531" s="7"/>
       <c r="H531" s="3"/>
     </row>
     <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A532" s="10"/>
+      <c r="A532" s="7"/>
       <c r="H532" s="3"/>
     </row>
     <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A533" s="10"/>
+      <c r="A533" s="7"/>
       <c r="H533" s="3"/>
     </row>
     <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A534" s="10"/>
+      <c r="A534" s="7"/>
       <c r="H534" s="3"/>
     </row>
     <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A535" s="10"/>
+      <c r="A535" s="7"/>
       <c r="H535" s="3"/>
     </row>
     <row r="536" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A536" s="10"/>
+      <c r="A536" s="7"/>
       <c r="H536" s="3"/>
     </row>
     <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="10"/>
+      <c r="A537" s="7"/>
       <c r="H537" s="3"/>
     </row>
     <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="10"/>
+      <c r="A538" s="7"/>
       <c r="H538" s="3"/>
     </row>
     <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A539" s="10"/>
+      <c r="A539" s="7"/>
       <c r="H539" s="3"/>
     </row>
     <row r="540" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A540" s="10"/>
+      <c r="A540" s="7"/>
       <c r="H540" s="3"/>
     </row>
     <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A541" s="10"/>
+      <c r="A541" s="7"/>
       <c r="H541" s="3"/>
     </row>
     <row r="542" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A542" s="10"/>
+      <c r="A542" s="7"/>
       <c r="H542" s="3"/>
     </row>
     <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A543" s="10"/>
+      <c r="A543" s="7"/>
       <c r="H543" s="3"/>
     </row>
     <row r="544" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A544" s="10"/>
+      <c r="A544" s="7"/>
       <c r="H544" s="3"/>
     </row>
     <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A545" s="10"/>
+      <c r="A545" s="7"/>
       <c r="H545" s="3"/>
     </row>
     <row r="546" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A546" s="10"/>
+      <c r="A546" s="7"/>
       <c r="H546" s="3"/>
     </row>
     <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A547" s="10"/>
+      <c r="A547" s="7"/>
       <c r="H547" s="3"/>
     </row>
     <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A548" s="10"/>
+      <c r="A548" s="7"/>
       <c r="H548" s="3"/>
     </row>
     <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A549" s="10"/>
+      <c r="A549" s="7"/>
       <c r="H549" s="3"/>
     </row>
     <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A550" s="10"/>
+      <c r="A550" s="7"/>
       <c r="H550" s="3"/>
     </row>
     <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A551" s="10"/>
+      <c r="A551" s="7"/>
       <c r="H551" s="3"/>
     </row>
     <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A552" s="10"/>
+      <c r="A552" s="7"/>
       <c r="H552" s="3"/>
     </row>
     <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A553" s="10"/>
+      <c r="A553" s="7"/>
       <c r="H553" s="3"/>
     </row>
     <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A554" s="10"/>
+      <c r="A554" s="7"/>
       <c r="H554" s="3"/>
     </row>
     <row r="555" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A555" s="10"/>
+      <c r="A555" s="7"/>
       <c r="H555" s="3"/>
     </row>
     <row r="556" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A556" s="10"/>
+      <c r="A556" s="7"/>
       <c r="H556" s="3"/>
     </row>
     <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A557" s="10"/>
+      <c r="A557" s="7"/>
       <c r="H557" s="3"/>
     </row>
     <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A558" s="10"/>
+      <c r="A558" s="7"/>
       <c r="H558" s="3"/>
     </row>
     <row r="559" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A559" s="10"/>
+      <c r="A559" s="7"/>
       <c r="H559" s="3"/>
     </row>
     <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="10"/>
+      <c r="A560" s="7"/>
       <c r="H560" s="3"/>
     </row>
     <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="10"/>
+      <c r="A561" s="7"/>
       <c r="H561" s="3"/>
     </row>
     <row r="562" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A562" s="10"/>
+      <c r="A562" s="7"/>
       <c r="H562" s="3"/>
     </row>
     <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A563" s="10"/>
+      <c r="A563" s="7"/>
       <c r="H563" s="3"/>
     </row>
     <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A564" s="10"/>
+      <c r="A564" s="7"/>
       <c r="H564" s="3"/>
     </row>
     <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A565" s="10"/>
+      <c r="A565" s="7"/>
       <c r="H565" s="3"/>
     </row>
     <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A566" s="10"/>
+      <c r="A566" s="7"/>
       <c r="H566" s="3"/>
     </row>
     <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A567" s="10"/>
+      <c r="A567" s="7"/>
       <c r="H567" s="3"/>
     </row>
     <row r="568" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A568" s="10"/>
+      <c r="A568" s="7"/>
       <c r="H568" s="3"/>
     </row>
     <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A569" s="10"/>
+      <c r="A569" s="7"/>
       <c r="H569" s="3"/>
     </row>
     <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A570" s="10"/>
+      <c r="A570" s="7"/>
       <c r="H570" s="3"/>
     </row>
     <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A571" s="10"/>
+      <c r="A571" s="7"/>
       <c r="H571" s="3"/>
     </row>
     <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A572" s="10"/>
+      <c r="A572" s="7"/>
       <c r="H572" s="3"/>
     </row>
     <row r="573" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A573" s="10"/>
+      <c r="A573" s="7"/>
       <c r="H573" s="3"/>
     </row>
     <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A574" s="10"/>
+      <c r="A574" s="7"/>
       <c r="H574" s="3"/>
     </row>
     <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A575" s="10"/>
+      <c r="A575" s="7"/>
       <c r="H575" s="3"/>
     </row>
     <row r="576" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A576" s="10"/>
+      <c r="A576" s="7"/>
       <c r="H576" s="3"/>
     </row>
     <row r="577" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A577" s="10"/>
+      <c r="A577" s="7"/>
       <c r="H577" s="3"/>
     </row>
     <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A578" s="10"/>
+      <c r="A578" s="7"/>
       <c r="H578" s="3"/>
     </row>
     <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A579" s="10"/>
+      <c r="A579" s="7"/>
       <c r="H579" s="3"/>
     </row>
     <row r="580" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A580" s="10"/>
+      <c r="A580" s="7"/>
       <c r="H580" s="3"/>
     </row>
     <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A581" s="10"/>
+      <c r="A581" s="7"/>
       <c r="H581" s="3"/>
     </row>
     <row r="582" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A582" s="10"/>
+      <c r="A582" s="7"/>
       <c r="H582" s="3"/>
     </row>
     <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A583" s="10"/>
+      <c r="A583" s="7"/>
       <c r="H583" s="3"/>
     </row>
     <row r="584" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A584" s="10"/>
+      <c r="A584" s="7"/>
       <c r="H584" s="3"/>
     </row>
     <row r="585" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A585" s="10"/>
+      <c r="A585" s="7"/>
       <c r="H585" s="3"/>
     </row>
     <row r="586" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A586" s="10"/>
+      <c r="A586" s="7"/>
       <c r="H586" s="3"/>
     </row>
     <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A587" s="10"/>
+      <c r="A587" s="7"/>
       <c r="H587" s="3"/>
     </row>
     <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A588" s="10"/>
+      <c r="A588" s="7"/>
       <c r="H588" s="3"/>
     </row>
     <row r="589" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A589" s="10"/>
+      <c r="A589" s="7"/>
       <c r="H589" s="3"/>
     </row>
     <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A590" s="10"/>
+      <c r="A590" s="7"/>
       <c r="H590" s="3"/>
     </row>
     <row r="591" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A591" s="10"/>
+      <c r="A591" s="7"/>
       <c r="H591" s="3"/>
     </row>
     <row r="592" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A592" s="10"/>
+      <c r="A592" s="7"/>
       <c r="H592" s="3"/>
     </row>
     <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A593" s="10"/>
+      <c r="A593" s="7"/>
       <c r="H593" s="3"/>
     </row>
     <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A594" s="10"/>
+      <c r="A594" s="7"/>
       <c r="H594" s="3"/>
     </row>
     <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A595" s="10"/>
+      <c r="A595" s="7"/>
       <c r="H595" s="3"/>
     </row>
     <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A596" s="10"/>
+      <c r="A596" s="7"/>
       <c r="H596" s="3"/>
     </row>
     <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="10"/>
+      <c r="A597" s="7"/>
       <c r="H597" s="3"/>
     </row>
     <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="10"/>
+      <c r="A598" s="7"/>
       <c r="H598" s="3"/>
     </row>
     <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A599" s="10"/>
+      <c r="A599" s="7"/>
       <c r="H599" s="3"/>
     </row>
     <row r="600" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A600" s="10"/>
+      <c r="A600" s="7"/>
       <c r="H600" s="3"/>
     </row>
     <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A601" s="10"/>
+      <c r="A601" s="7"/>
       <c r="H601" s="3"/>
     </row>
     <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A602" s="10"/>
+      <c r="A602" s="7"/>
       <c r="H602" s="3"/>
     </row>
     <row r="603" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A603" s="10"/>
+      <c r="A603" s="7"/>
       <c r="H603" s="3"/>
     </row>
     <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A604" s="10"/>
+      <c r="A604" s="7"/>
       <c r="H604" s="3"/>
     </row>
     <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A605" s="10"/>
+      <c r="A605" s="7"/>
       <c r="H605" s="3"/>
     </row>
     <row r="606" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A606" s="10"/>
+      <c r="A606" s="7"/>
       <c r="H606" s="3"/>
     </row>
     <row r="607" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="10"/>
+      <c r="A607" s="7"/>
       <c r="H607" s="3"/>
     </row>
     <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="10"/>
+      <c r="A608" s="7"/>
       <c r="H608" s="3"/>
     </row>
     <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A609" s="10"/>
+      <c r="A609" s="7"/>
       <c r="H609" s="3"/>
     </row>
     <row r="610" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A610" s="10"/>
+      <c r="A610" s="7"/>
       <c r="H610" s="3"/>
     </row>
     <row r="611" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A611" s="10"/>
+      <c r="A611" s="7"/>
       <c r="H611" s="3"/>
     </row>
     <row r="612" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A612" s="10"/>
+      <c r="A612" s="7"/>
       <c r="H612" s="3"/>
     </row>
     <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A613" s="10"/>
+      <c r="A613" s="7"/>
       <c r="H613" s="3"/>
     </row>
     <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="10"/>
+      <c r="A614" s="7"/>
       <c r="H614" s="3"/>
     </row>
     <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="10"/>
+      <c r="A615" s="7"/>
       <c r="H615" s="3"/>
     </row>
     <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A616" s="10"/>
+      <c r="A616" s="7"/>
       <c r="H616" s="3"/>
     </row>
     <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A617" s="10"/>
+      <c r="A617" s="7"/>
       <c r="H617" s="3"/>
     </row>
     <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A618" s="10"/>
+      <c r="A618" s="7"/>
       <c r="H618" s="3"/>
     </row>
     <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A619" s="10"/>
+      <c r="A619" s="7"/>
       <c r="H619" s="3"/>
     </row>
     <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A620" s="10"/>
+      <c r="A620" s="7"/>
       <c r="H620" s="3"/>
     </row>
     <row r="621" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A621" s="10"/>
+      <c r="A621" s="7"/>
       <c r="H621" s="3"/>
     </row>
     <row r="622" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A622" s="10"/>
+      <c r="A622" s="7"/>
       <c r="H622" s="3"/>
     </row>
     <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A623" s="10"/>
+      <c r="A623" s="7"/>
       <c r="H623" s="3"/>
     </row>
     <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A624" s="10"/>
+      <c r="A624" s="7"/>
       <c r="H624" s="3"/>
     </row>
     <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A625" s="10"/>
+      <c r="A625" s="7"/>
       <c r="H625" s="3"/>
     </row>
     <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A626" s="10"/>
+      <c r="A626" s="7"/>
       <c r="H626" s="3"/>
     </row>
     <row r="627" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A627" s="10"/>
+      <c r="A627" s="7"/>
       <c r="H627" s="3"/>
     </row>
     <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A628" s="10"/>
+      <c r="A628" s="7"/>
       <c r="H628" s="3"/>
     </row>
     <row r="629" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A629" s="10"/>
+      <c r="A629" s="7"/>
       <c r="H629" s="3"/>
     </row>
     <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A630" s="10"/>
+      <c r="A630" s="7"/>
       <c r="H630" s="3"/>
     </row>
     <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A631" s="10"/>
+      <c r="A631" s="7"/>
       <c r="H631" s="3"/>
     </row>
     <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A632" s="10"/>
+      <c r="A632" s="7"/>
       <c r="H632" s="3"/>
     </row>
     <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A633" s="10"/>
+      <c r="A633" s="7"/>
       <c r="H633" s="3"/>
     </row>
     <row r="634" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A634" s="10"/>
+      <c r="A634" s="7"/>
       <c r="H634" s="3"/>
     </row>
     <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A635" s="10"/>
+      <c r="A635" s="7"/>
       <c r="H635" s="3"/>
     </row>
     <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A636" s="10"/>
+      <c r="A636" s="7"/>
       <c r="H636" s="3"/>
     </row>
     <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A637" s="10"/>
+      <c r="A637" s="7"/>
       <c r="H637" s="3"/>
     </row>
     <row r="638" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A638" s="10"/>
+      <c r="A638" s="7"/>
       <c r="H638" s="3"/>
     </row>
     <row r="639" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A639" s="10"/>
+      <c r="A639" s="7"/>
       <c r="H639" s="3"/>
     </row>
     <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A640" s="10"/>
+      <c r="A640" s="7"/>
       <c r="H640" s="3"/>
     </row>
     <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A641" s="10"/>
+      <c r="A641" s="7"/>
       <c r="H641" s="3"/>
     </row>
     <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A642" s="10"/>
+      <c r="A642" s="7"/>
       <c r="H642" s="3"/>
     </row>
     <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A643" s="10"/>
+      <c r="A643" s="7"/>
       <c r="H643" s="3"/>
     </row>
     <row r="644" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A644" s="10"/>
+      <c r="A644" s="7"/>
       <c r="H644" s="3"/>
     </row>
     <row r="645" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A645" s="10"/>
+      <c r="A645" s="7"/>
       <c r="H645" s="3"/>
     </row>
     <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A646" s="10"/>
+      <c r="A646" s="7"/>
       <c r="H646" s="3"/>
     </row>
     <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A647" s="10"/>
+      <c r="A647" s="7"/>
       <c r="H647" s="3"/>
     </row>
   </sheetData>
@@ -7394,2361 +7091,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791C0AD6-8799-4D8E-ACC2-485BF8DEB0B4}">
-  <dimension ref="A1:F150"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.796875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="5"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="6">
-        <v>159.77000000000001</v>
-      </c>
-      <c r="D2" s="7">
-        <v>2542650</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="6">
-        <v>47.02</v>
-      </c>
-      <c r="D3" s="7">
-        <v>1527600</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="6">
-        <v>47.02</v>
-      </c>
-      <c r="D4" s="7">
-        <v>1688400</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="6">
-        <v>42.55</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1628100</v>
-      </c>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="6">
-        <v>41.74</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1487400</v>
-      </c>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="6">
-        <v>52.16</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1788900</v>
-      </c>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="6">
-        <v>33.340000000000003</v>
-      </c>
-      <c r="D8" s="7">
-        <v>864300</v>
-      </c>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="6">
-        <v>48.4</v>
-      </c>
-      <c r="D9" s="7">
-        <v>924600</v>
-      </c>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="6">
-        <v>31.36</v>
-      </c>
-      <c r="D10" s="7">
-        <v>683400</v>
-      </c>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="6">
-        <v>31.01</v>
-      </c>
-      <c r="D11" s="7">
-        <v>683400</v>
-      </c>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="6">
-        <v>30.95</v>
-      </c>
-      <c r="D12" s="7">
-        <v>683400</v>
-      </c>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="6">
-        <v>31.3</v>
-      </c>
-      <c r="D13" s="7">
-        <v>683400</v>
-      </c>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="6">
-        <v>45.26</v>
-      </c>
-      <c r="D14" s="7">
-        <v>934650</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="6">
-        <v>40.07</v>
-      </c>
-      <c r="D15" s="7">
-        <v>874350</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="6">
-        <v>30.42</v>
-      </c>
-      <c r="D16" s="7">
-        <v>773850</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="6">
-        <v>33.17</v>
-      </c>
-      <c r="D17" s="7">
-        <v>783900</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" s="6">
-        <v>23.27</v>
-      </c>
-      <c r="D18" s="7">
-        <v>668325</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="6">
-        <v>22.59</v>
-      </c>
-      <c r="D19" s="7">
-        <v>668325</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="6">
-        <v>26.44</v>
-      </c>
-      <c r="D20" s="7">
-        <v>733650</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="6">
-        <v>26.44</v>
-      </c>
-      <c r="D21" s="7">
-        <v>733650</v>
-      </c>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="6">
-        <v>26.44</v>
-      </c>
-      <c r="D22" s="7">
-        <v>733650</v>
-      </c>
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="6">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="D23" s="7">
-        <v>783900</v>
-      </c>
-      <c r="E23" s="6"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="6">
-        <v>42.54</v>
-      </c>
-      <c r="D24" s="7">
-        <v>1035150</v>
-      </c>
-      <c r="E24" s="6"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="6">
-        <v>36.630000000000003</v>
-      </c>
-      <c r="D25" s="7">
-        <v>924600</v>
-      </c>
-      <c r="E25" s="6"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="6">
-        <v>26.78</v>
-      </c>
-      <c r="D26" s="7">
-        <v>763800</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="6">
-        <v>29.67</v>
-      </c>
-      <c r="D27" s="7">
-        <v>783900</v>
-      </c>
-      <c r="E27" s="6"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="6">
-        <v>30.16</v>
-      </c>
-      <c r="D28" s="7">
-        <v>783900</v>
-      </c>
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="6">
-        <v>30.61</v>
-      </c>
-      <c r="D29" s="7">
-        <v>783900</v>
-      </c>
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="6">
-        <v>24.47</v>
-      </c>
-      <c r="D30" s="7">
-        <v>723600</v>
-      </c>
-      <c r="E30" s="6"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="6">
-        <v>25.06</v>
-      </c>
-      <c r="D31" s="7">
-        <v>693450</v>
-      </c>
-      <c r="E31" s="6"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="6">
-        <v>30.61</v>
-      </c>
-      <c r="D32" s="7">
-        <v>824100</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="6">
-        <v>30.61</v>
-      </c>
-      <c r="D33" s="7">
-        <v>824100</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="6">
-        <v>25.06</v>
-      </c>
-      <c r="D34" s="7">
-        <v>743700</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="6">
-        <v>33.24</v>
-      </c>
-      <c r="D35" s="7">
-        <v>824100</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" s="6">
-        <v>109.32</v>
-      </c>
-      <c r="D36" s="7">
-        <v>824823.5</v>
-      </c>
-      <c r="E36" s="6"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="6">
-        <v>184.21</v>
-      </c>
-      <c r="D37" s="7">
-        <v>3139359.78</v>
-      </c>
-      <c r="E37" s="6"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="6">
-        <v>188.27</v>
-      </c>
-      <c r="D38" s="7">
-        <v>3208551.46</v>
-      </c>
-      <c r="E38" s="6"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="6">
-        <v>84.81</v>
-      </c>
-      <c r="D39" s="7">
-        <v>748184.49</v>
-      </c>
-      <c r="E39" s="6"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="6">
-        <v>90.86</v>
-      </c>
-      <c r="D40" s="7">
-        <v>759369.72</v>
-      </c>
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="6">
-        <v>85.3</v>
-      </c>
-      <c r="D41" s="7">
-        <v>742605.81</v>
-      </c>
-      <c r="E41" s="6"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="6">
-        <v>113.07</v>
-      </c>
-      <c r="D42" s="7">
-        <v>891298.86</v>
-      </c>
-      <c r="E42" s="6"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" s="6">
-        <v>84.41</v>
-      </c>
-      <c r="D43" s="7">
-        <v>761579.73</v>
-      </c>
-      <c r="E43" s="6"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" s="6">
-        <v>120.48</v>
-      </c>
-      <c r="D44" s="7">
-        <v>1107994.77</v>
-      </c>
-      <c r="E44" s="6"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="6">
-        <v>89.93</v>
-      </c>
-      <c r="D45" s="7">
-        <v>730244.98</v>
-      </c>
-      <c r="E45" s="6"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="6">
-        <v>78.42</v>
-      </c>
-      <c r="D46" s="7">
-        <v>700915.41</v>
-      </c>
-      <c r="E46" s="6"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="6">
-        <v>66.28</v>
-      </c>
-      <c r="D47" s="7">
-        <v>730893.59</v>
-      </c>
-      <c r="E47" s="6"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C48" s="6">
-        <v>154.47999999999999</v>
-      </c>
-      <c r="D48" s="7">
-        <v>2942421.11</v>
-      </c>
-      <c r="E48" s="6"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C49" s="6">
-        <v>155.79</v>
-      </c>
-      <c r="D49" s="7">
-        <v>2967373.02</v>
-      </c>
-      <c r="E49" s="6"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C50" s="6">
-        <v>68.349999999999994</v>
-      </c>
-      <c r="D50" s="7">
-        <v>753720.22</v>
-      </c>
-      <c r="E50" s="6"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C51" s="6">
-        <v>68.459999999999994</v>
-      </c>
-      <c r="D51" s="7">
-        <v>754933.24</v>
-      </c>
-      <c r="E51" s="6"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" s="6">
-        <v>65.790000000000006</v>
-      </c>
-      <c r="D52" s="7">
-        <v>725490.18</v>
-      </c>
-      <c r="E52" s="6"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" s="6">
-        <v>93.55</v>
-      </c>
-      <c r="D53" s="7">
-        <v>844044.35</v>
-      </c>
-      <c r="E53" s="6"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C54" s="6">
-        <v>84.41</v>
-      </c>
-      <c r="D54" s="7">
-        <v>803889.71</v>
-      </c>
-      <c r="E54" s="6"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C55" s="6">
-        <v>100.14</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1054085.53</v>
-      </c>
-      <c r="E55" s="6"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C56" s="6">
-        <v>74.61</v>
-      </c>
-      <c r="D56" s="7">
-        <v>710558.13</v>
-      </c>
-      <c r="E56" s="6"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C57" s="6">
-        <v>64.069999999999993</v>
-      </c>
-      <c r="D57" s="7">
-        <v>706523.11</v>
-      </c>
-      <c r="E57" s="6"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C58" s="6">
-        <v>66.28</v>
-      </c>
-      <c r="D58" s="7">
-        <v>769362</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C59" s="6">
-        <v>154.47999999999999</v>
-      </c>
-      <c r="D59" s="7">
-        <v>3097285</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C60" s="6">
-        <v>155.79</v>
-      </c>
-      <c r="D60" s="7">
-        <v>3123551</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C61" s="6">
-        <v>68.349999999999994</v>
-      </c>
-      <c r="D61" s="7">
-        <v>793390</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C62" s="6">
-        <v>68.459999999999994</v>
-      </c>
-      <c r="D62" s="7">
-        <v>794667</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C63" s="6">
-        <v>65.790000000000006</v>
-      </c>
-      <c r="D63" s="7">
-        <v>763674</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C64" s="6">
-        <v>93.55</v>
-      </c>
-      <c r="D64" s="7">
-        <v>888468</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C65" s="6">
-        <v>84.41</v>
-      </c>
-      <c r="D65" s="7">
-        <v>846200</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C66" s="6">
-        <v>100.14</v>
-      </c>
-      <c r="D66" s="7">
-        <v>1109564</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C67" s="6">
-        <v>74.61</v>
-      </c>
-      <c r="D67" s="7">
-        <v>747956</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C68" s="6">
-        <v>64.069999999999993</v>
-      </c>
-      <c r="D68" s="7">
-        <v>743709</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C69" s="6">
-        <v>66.28</v>
-      </c>
-      <c r="D69" s="7">
-        <v>807829.75</v>
-      </c>
-      <c r="E69" s="6"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C70" s="6">
-        <v>154.47999999999999</v>
-      </c>
-      <c r="D70" s="7">
-        <v>3252149.65</v>
-      </c>
-      <c r="E70" s="6"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C71" s="6">
-        <v>155.79</v>
-      </c>
-      <c r="D71" s="7">
-        <v>3279728.08</v>
-      </c>
-      <c r="E71" s="6"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C72" s="6">
-        <v>68.349999999999994</v>
-      </c>
-      <c r="D72" s="7">
-        <v>833059.19</v>
-      </c>
-      <c r="E72" s="6"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C73" s="6">
-        <v>68.459999999999994</v>
-      </c>
-      <c r="D73" s="7">
-        <v>834399.89</v>
-      </c>
-      <c r="E73" s="6"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C74" s="6">
-        <v>65.790000000000006</v>
-      </c>
-      <c r="D74" s="7">
-        <v>801857.57</v>
-      </c>
-      <c r="E74" s="6"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C75" s="6">
-        <v>93.55</v>
-      </c>
-      <c r="D75" s="7">
-        <v>932891.13</v>
-      </c>
-      <c r="E75" s="6"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C76" s="6">
-        <v>84.41</v>
-      </c>
-      <c r="D76" s="7">
-        <v>888509.69</v>
-      </c>
-      <c r="E76" s="6"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C77" s="6">
-        <v>100.14</v>
-      </c>
-      <c r="D77" s="7">
-        <v>1165041.9099999999</v>
-      </c>
-      <c r="E77" s="6"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C78" s="6">
-        <v>74.61</v>
-      </c>
-      <c r="D78" s="7">
-        <v>785353.72</v>
-      </c>
-      <c r="E78" s="6"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C79" s="6">
-        <v>64.069999999999993</v>
-      </c>
-      <c r="D79" s="7">
-        <v>780893.96</v>
-      </c>
-      <c r="E79" s="6"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C80" s="6">
-        <v>66.28</v>
-      </c>
-      <c r="D80" s="7">
-        <v>846297.84</v>
-      </c>
-      <c r="E80" s="6"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C81" s="6">
-        <v>154.47999999999999</v>
-      </c>
-      <c r="D81" s="7">
-        <v>3407013.92</v>
-      </c>
-      <c r="E81" s="6"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C82" s="6">
-        <v>155.79</v>
-      </c>
-      <c r="D82" s="7">
-        <v>3435906</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C83" s="6">
-        <v>68.349999999999994</v>
-      </c>
-      <c r="D83" s="7">
-        <v>872728.68</v>
-      </c>
-      <c r="E83" s="6"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C84" s="6">
-        <v>68.459999999999994</v>
-      </c>
-      <c r="D84" s="7">
-        <v>874133.22</v>
-      </c>
-      <c r="E84" s="6"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C85" s="6">
-        <v>65.790000000000006</v>
-      </c>
-      <c r="D85" s="7">
-        <v>840041.26</v>
-      </c>
-      <c r="E85" s="6"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C86" s="6">
-        <v>93.55</v>
-      </c>
-      <c r="D86" s="7">
-        <v>977314.51</v>
-      </c>
-      <c r="E86" s="6"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C87" s="6">
-        <v>84.41</v>
-      </c>
-      <c r="D87" s="7">
-        <v>930819.66</v>
-      </c>
-      <c r="E87" s="6"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C88" s="6">
-        <v>100.14</v>
-      </c>
-      <c r="D88" s="7">
-        <v>1220520.0900000001</v>
-      </c>
-      <c r="E88" s="6"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C89" s="6">
-        <v>74.61</v>
-      </c>
-      <c r="D89" s="7">
-        <v>822751.51</v>
-      </c>
-      <c r="E89" s="6"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C90" s="6">
-        <v>64.069999999999993</v>
-      </c>
-      <c r="D90" s="7">
-        <v>818079.4</v>
-      </c>
-      <c r="E90" s="6"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C91" s="6">
-        <v>90.03</v>
-      </c>
-      <c r="D91" s="7">
-        <v>778084.04</v>
-      </c>
-      <c r="E91" s="6"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C92" s="6">
-        <v>147.04</v>
-      </c>
-      <c r="D92" s="7">
-        <v>2505897.9500000002</v>
-      </c>
-      <c r="E92" s="6"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C93" s="6">
-        <v>142.78</v>
-      </c>
-      <c r="D93" s="7">
-        <v>2576432.9700000002</v>
-      </c>
-      <c r="E93" s="6"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C94" s="6">
-        <v>89.06</v>
-      </c>
-      <c r="D94" s="7">
-        <v>1311028.8799999999</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C95" s="6">
-        <v>89.08</v>
-      </c>
-      <c r="D95" s="7">
-        <v>1269022.55</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C96" s="6">
-        <v>88.91</v>
-      </c>
-      <c r="D96" s="7">
-        <v>1224380.72</v>
-      </c>
-      <c r="E96" s="6"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C97" s="6">
-        <v>104.2</v>
-      </c>
-      <c r="D97" s="7">
-        <v>1385458.83</v>
-      </c>
-      <c r="E97" s="6"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C98" s="6">
-        <v>92.79</v>
-      </c>
-      <c r="D98" s="7">
-        <v>793124.84</v>
-      </c>
-      <c r="E98" s="6"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C99" s="6">
-        <v>93.1</v>
-      </c>
-      <c r="D99" s="7">
-        <v>813458.46</v>
-      </c>
-      <c r="E99" s="6"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C100" s="6">
-        <v>138.04</v>
-      </c>
-      <c r="D100" s="7">
-        <v>1194467.02</v>
-      </c>
-      <c r="E100" s="6"/>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C101" s="6">
-        <v>128.11000000000001</v>
-      </c>
-      <c r="D101" s="7">
-        <v>949020.3</v>
-      </c>
-      <c r="E101" s="6"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C102" s="6">
-        <v>89.49</v>
-      </c>
-      <c r="D102" s="7">
-        <v>753585.89</v>
-      </c>
-      <c r="E102" s="6"/>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C103" s="6">
-        <v>73.87</v>
-      </c>
-      <c r="D103" s="7">
-        <v>777564.39</v>
-      </c>
-      <c r="E103" s="6"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C104" s="6">
-        <v>124.71</v>
-      </c>
-      <c r="D104" s="7">
-        <v>2375384.1</v>
-      </c>
-      <c r="E104" s="6"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C105" s="6">
-        <v>142.78</v>
-      </c>
-      <c r="D105" s="7">
-        <v>2719568.14</v>
-      </c>
-      <c r="E105" s="6"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C106" s="6">
-        <v>89.06</v>
-      </c>
-      <c r="D106" s="7">
-        <v>1383863.82</v>
-      </c>
-      <c r="E106" s="6"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C107" s="6">
-        <v>89.08</v>
-      </c>
-      <c r="D107" s="7">
-        <v>1339523.8</v>
-      </c>
-      <c r="E107" s="6"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C108" s="6">
-        <v>88.91</v>
-      </c>
-      <c r="D108" s="7">
-        <v>1292401.8700000001</v>
-      </c>
-      <c r="E108" s="6"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C109" s="6">
-        <v>104.2</v>
-      </c>
-      <c r="D109" s="7">
-        <v>1462428.77</v>
-      </c>
-      <c r="E109" s="6"/>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C110" s="6">
-        <v>92.79</v>
-      </c>
-      <c r="D110" s="7">
-        <v>837187.34</v>
-      </c>
-      <c r="E110" s="6"/>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C111" s="6">
-        <v>93.1</v>
-      </c>
-      <c r="D111" s="7">
-        <v>858650.59</v>
-      </c>
-      <c r="E111" s="6"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C112" s="6">
-        <v>113.74</v>
-      </c>
-      <c r="D112" s="7">
-        <v>1140229.28</v>
-      </c>
-      <c r="E112" s="6"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C113" s="6">
-        <v>101.16</v>
-      </c>
-      <c r="D113" s="7">
-        <v>912704.72</v>
-      </c>
-      <c r="E113" s="6"/>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C114" s="6">
-        <v>71.86</v>
-      </c>
-      <c r="D114" s="7">
-        <v>756406.9</v>
-      </c>
-      <c r="E114" s="6"/>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C115" s="6">
-        <v>73.87</v>
-      </c>
-      <c r="D115" s="7">
-        <v>818489</v>
-      </c>
-      <c r="E115" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C116" s="6">
-        <v>124.71</v>
-      </c>
-      <c r="D116" s="7">
-        <v>2500404</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C117" s="6">
-        <v>142.78</v>
-      </c>
-      <c r="D117" s="7">
-        <v>2862703</v>
-      </c>
-      <c r="E117" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C118" s="6">
-        <v>89.06</v>
-      </c>
-      <c r="D118" s="7">
-        <v>1456699</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C119" s="6">
-        <v>89.08</v>
-      </c>
-      <c r="D119" s="7">
-        <v>1410025</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C120" s="6">
-        <v>88.91</v>
-      </c>
-      <c r="D120" s="7">
-        <v>1360423</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C121" s="6">
-        <v>104.2</v>
-      </c>
-      <c r="D121" s="7">
-        <v>1539399</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C122" s="6">
-        <v>92.79</v>
-      </c>
-      <c r="D122" s="7">
-        <v>881250</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C123" s="6">
-        <v>93.1</v>
-      </c>
-      <c r="D123" s="7">
-        <v>903843</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C124" s="6">
-        <v>113.74</v>
-      </c>
-      <c r="D124" s="7">
-        <v>1200241</v>
-      </c>
-      <c r="E124" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C125" s="6">
-        <v>101.16</v>
-      </c>
-      <c r="D125" s="7">
-        <v>960742</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C126" s="6">
-        <v>71.86</v>
-      </c>
-      <c r="D126" s="7">
-        <v>796218</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C127" s="6">
-        <v>73.87</v>
-      </c>
-      <c r="D127" s="7">
-        <v>859413.28</v>
-      </c>
-      <c r="E127" s="6"/>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C128" s="6">
-        <v>124.71</v>
-      </c>
-      <c r="D128" s="7">
-        <v>2625424.54</v>
-      </c>
-      <c r="E128" s="6"/>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C129" s="6">
-        <v>142.78</v>
-      </c>
-      <c r="D129" s="7">
-        <v>3005838.47</v>
-      </c>
-      <c r="E129" s="6"/>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C130" s="6">
-        <v>89.06</v>
-      </c>
-      <c r="D130" s="7">
-        <v>1529533.69</v>
-      </c>
-      <c r="E130" s="6"/>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C131" s="6">
-        <v>89.08</v>
-      </c>
-      <c r="D131" s="7">
-        <v>1480526.3</v>
-      </c>
-      <c r="E131" s="6"/>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C132" s="6">
-        <v>88.91</v>
-      </c>
-      <c r="D132" s="7">
-        <v>1428444.18</v>
-      </c>
-      <c r="E132" s="6"/>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C133" s="6">
-        <v>104.2</v>
-      </c>
-      <c r="D133" s="7">
-        <v>1616368.6399999999</v>
-      </c>
-      <c r="E133" s="6"/>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C134" s="6">
-        <v>92.79</v>
-      </c>
-      <c r="D134" s="7">
-        <v>925312.32</v>
-      </c>
-      <c r="E134" s="6"/>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="C135" s="6">
-        <v>93.1</v>
-      </c>
-      <c r="D135" s="7">
-        <v>949034.87</v>
-      </c>
-      <c r="E135" s="6"/>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C136" s="6">
-        <v>113.74</v>
-      </c>
-      <c r="D136" s="7">
-        <v>1260253.42</v>
-      </c>
-      <c r="E136" s="6"/>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C137" s="6">
-        <v>101.16</v>
-      </c>
-      <c r="D137" s="7">
-        <v>1008778.9</v>
-      </c>
-      <c r="E137" s="6"/>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C138" s="6">
-        <v>71.86</v>
-      </c>
-      <c r="D138" s="7">
-        <v>836028.67</v>
-      </c>
-      <c r="E138" s="6"/>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="C139" s="6">
-        <v>73.87</v>
-      </c>
-      <c r="D139" s="7">
-        <v>900337.72</v>
-      </c>
-      <c r="E139" s="6"/>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C140" s="6">
-        <v>124.71</v>
-      </c>
-      <c r="D140" s="7">
-        <v>2750444.75</v>
-      </c>
-      <c r="E140" s="6"/>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C141" s="6">
-        <v>142.78</v>
-      </c>
-      <c r="D141" s="7">
-        <v>3148973.64</v>
-      </c>
-      <c r="E141" s="6"/>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C142" s="6">
-        <v>89.06</v>
-      </c>
-      <c r="D142" s="7">
-        <v>1602368.63</v>
-      </c>
-      <c r="E142" s="6"/>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C143" s="6">
-        <v>89.08</v>
-      </c>
-      <c r="D143" s="7">
-        <v>1551027.56</v>
-      </c>
-      <c r="E143" s="6"/>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C144" s="6">
-        <v>88.91</v>
-      </c>
-      <c r="D144" s="7">
-        <v>1496465.33</v>
-      </c>
-      <c r="E144" s="6"/>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C145" s="6">
-        <v>104.2</v>
-      </c>
-      <c r="D145" s="7">
-        <v>1693338.57</v>
-      </c>
-      <c r="E145" s="6"/>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C146" s="6">
-        <v>92.79</v>
-      </c>
-      <c r="D146" s="7">
-        <v>969374.81</v>
-      </c>
-      <c r="E146" s="6"/>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C147" s="6">
-        <v>93.1</v>
-      </c>
-      <c r="D147" s="7">
-        <v>994227</v>
-      </c>
-      <c r="E147" s="6"/>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C148" s="6">
-        <v>113.74</v>
-      </c>
-      <c r="D148" s="7">
-        <v>1320265.49</v>
-      </c>
-      <c r="E148" s="6"/>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C149" s="6">
-        <v>101.16</v>
-      </c>
-      <c r="D149" s="7">
-        <v>1056815.99</v>
-      </c>
-      <c r="E149" s="6"/>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C150" s="6">
-        <v>71.86</v>
-      </c>
-      <c r="D150" s="7">
-        <v>875839.56</v>
-      </c>
-      <c r="E150" s="6"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E150" xr:uid="{791C0AD6-8799-4D8E-ACC2-485BF8DEB0B4}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5712544-8F9D-45CB-9B02-6C1DF06DB87F}">
   <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -9798,7 +7140,7 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>272</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
@@ -9816,7 +7158,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>

--- a/modelo-painel-vendas.xlsx
+++ b/modelo-painel-vendas.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061EF26C-AF64-48E8-BA79-9F289E460106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unidades" sheetId="1" r:id="rId1"/>

--- a/modelo-painel-vendas.xlsx
+++ b/modelo-painel-vendas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip\OneDrive\Área de Trabalho\SALES DASHBOARD - CLAUDE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061EF26C-AF64-48E8-BA79-9F289E460106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1733FD8-240B-4F22-8F7D-716ED213EFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Instruções" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unidades!$A$1:$I$647</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unidades!$A$1:$I$648</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Unidades!$C$1:$H$140</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="182">
   <si>
     <t>Empreendimento</t>
   </si>
@@ -574,6 +574,15 @@
   </si>
   <si>
     <t>Marilene</t>
+  </si>
+  <si>
+    <t>Ricardo Aparecido da Silva</t>
+  </si>
+  <si>
+    <t>210 - BL 1</t>
+  </si>
+  <si>
+    <t>Plano 24x</t>
   </si>
 </sst>
 </file>
@@ -1004,8 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:J647"/>
+  <dimension ref="A1:J651"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5" style="1" bestFit="1" customWidth="1"/>
@@ -1053,7 +1061,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>44958</v>
       </c>
@@ -1081,7 +1089,7 @@
       </c>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>44958</v>
       </c>
@@ -1109,7 +1117,7 @@
       </c>
       <c r="J3" s="6"/>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>45292</v>
       </c>
@@ -1137,7 +1145,7 @@
       </c>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>45352</v>
       </c>
@@ -1165,7 +1173,7 @@
       </c>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>44621</v>
       </c>
@@ -1193,7 +1201,7 @@
       </c>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>44958</v>
       </c>
@@ -1221,7 +1229,7 @@
       </c>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>44621</v>
       </c>
@@ -1249,7 +1257,7 @@
       </c>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>44652</v>
       </c>
@@ -1277,7 +1285,7 @@
       </c>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>44652</v>
       </c>
@@ -1305,7 +1313,7 @@
       </c>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>45292</v>
       </c>
@@ -1333,7 +1341,7 @@
       </c>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>44927</v>
       </c>
@@ -1361,7 +1369,7 @@
       </c>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>45292</v>
       </c>
@@ -1389,7 +1397,7 @@
       </c>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>45231</v>
       </c>
@@ -1417,7 +1425,7 @@
       </c>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>44866</v>
       </c>
@@ -1445,7 +1453,7 @@
       </c>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>44621</v>
       </c>
@@ -1473,7 +1481,7 @@
       </c>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>44621</v>
       </c>
@@ -1501,7 +1509,7 @@
       </c>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>44927</v>
       </c>
@@ -1529,7 +1537,7 @@
       </c>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>44621</v>
       </c>
@@ -1557,7 +1565,7 @@
       </c>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>44621</v>
       </c>
@@ -1585,7 +1593,7 @@
       </c>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>44682</v>
       </c>
@@ -1613,7 +1621,7 @@
       </c>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>44621</v>
       </c>
@@ -1641,7 +1649,7 @@
       </c>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>44774</v>
       </c>
@@ -1669,7 +1677,7 @@
       </c>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>44896</v>
       </c>
@@ -1697,7 +1705,7 @@
       </c>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>44927</v>
       </c>
@@ -1725,7 +1733,7 @@
       </c>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>44835</v>
       </c>
@@ -1753,7 +1761,7 @@
       </c>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>45139</v>
       </c>
@@ -1781,7 +1789,7 @@
       </c>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>44958</v>
       </c>
@@ -1809,7 +1817,7 @@
       </c>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>45352</v>
       </c>
@@ -1837,7 +1845,7 @@
       </c>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>45406</v>
       </c>
@@ -1865,7 +1873,7 @@
       </c>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>45352</v>
       </c>
@@ -1893,7 +1901,7 @@
       </c>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>45387</v>
       </c>
@@ -1921,7 +1929,7 @@
       </c>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>45323</v>
       </c>
@@ -1949,7 +1957,7 @@
       </c>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>45352</v>
       </c>
@@ -1975,7 +1983,7 @@
       </c>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>45386</v>
       </c>
@@ -2001,7 +2009,7 @@
       </c>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>45323</v>
       </c>
@@ -2027,7 +2035,7 @@
       </c>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>45352</v>
       </c>
@@ -2053,7 +2061,7 @@
       </c>
       <c r="J37" s="6"/>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>45413</v>
       </c>
@@ -2081,7 +2089,7 @@
       </c>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>45413</v>
       </c>
@@ -2109,7 +2117,7 @@
       </c>
       <c r="J39" s="6"/>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>45413</v>
       </c>
@@ -2137,7 +2145,7 @@
       </c>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>45474</v>
       </c>
@@ -2165,7 +2173,7 @@
       </c>
       <c r="J41" s="6"/>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>45499</v>
       </c>
@@ -2191,7 +2199,7 @@
       </c>
       <c r="J42" s="6"/>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>45534</v>
       </c>
@@ -2217,7 +2225,7 @@
       </c>
       <c r="J43" s="6"/>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>45579</v>
       </c>
@@ -2245,7 +2253,7 @@
       </c>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>45573</v>
       </c>
@@ -2273,7 +2281,7 @@
       </c>
       <c r="J45" s="6"/>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <v>45576</v>
       </c>
@@ -2301,7 +2309,7 @@
       </c>
       <c r="J46" s="6"/>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>45566</v>
       </c>
@@ -2329,7 +2337,7 @@
       </c>
       <c r="J47" s="6"/>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>45566</v>
       </c>
@@ -2357,7 +2365,7 @@
       </c>
       <c r="J48" s="6"/>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>45581</v>
       </c>
@@ -2385,7 +2393,7 @@
       </c>
       <c r="J49" s="6"/>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>45603</v>
       </c>
@@ -2413,7 +2421,7 @@
       </c>
       <c r="J50" s="6"/>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>45644</v>
       </c>
@@ -2441,7 +2449,7 @@
       </c>
       <c r="J51" s="6"/>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>45659</v>
       </c>
@@ -2469,7 +2477,7 @@
       </c>
       <c r="J52" s="6"/>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>45659</v>
       </c>
@@ -2497,7 +2505,7 @@
       </c>
       <c r="J53" s="6"/>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>45659</v>
       </c>
@@ -2523,7 +2531,7 @@
       </c>
       <c r="J54" s="6"/>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>45679</v>
       </c>
@@ -2551,7 +2559,7 @@
       </c>
       <c r="J55" s="6"/>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>45713</v>
       </c>
@@ -2579,7 +2587,7 @@
       </c>
       <c r="J56" s="6"/>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>45726</v>
       </c>
@@ -2607,7 +2615,7 @@
       </c>
       <c r="J57" s="6"/>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>45724</v>
       </c>
@@ -2635,7 +2643,7 @@
       </c>
       <c r="J58" s="6"/>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>45726</v>
       </c>
@@ -2663,7 +2671,7 @@
       </c>
       <c r="J59" s="6"/>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>45738</v>
       </c>
@@ -2691,7 +2699,7 @@
       </c>
       <c r="J60" s="6"/>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>45783</v>
       </c>
@@ -2719,7 +2727,7 @@
       </c>
       <c r="J61" s="6"/>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>45860</v>
       </c>
@@ -2745,7 +2753,7 @@
       </c>
       <c r="J62" s="6"/>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>45888</v>
       </c>
@@ -2771,7 +2779,7 @@
       </c>
       <c r="J63" s="6"/>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>45909</v>
       </c>
@@ -2799,7 +2807,7 @@
       </c>
       <c r="J64" s="6"/>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>45909</v>
       </c>
@@ -2827,7 +2835,7 @@
       </c>
       <c r="J65" s="6"/>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>45954</v>
       </c>
@@ -2853,7 +2861,7 @@
       </c>
       <c r="J66" s="6"/>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>45966</v>
       </c>
@@ -2881,7 +2889,7 @@
       </c>
       <c r="J67" s="6"/>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>46028</v>
       </c>
@@ -2907,7 +2915,7 @@
       </c>
       <c r="J68" s="6"/>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <v>46031</v>
       </c>
@@ -2933,7 +2941,7 @@
       </c>
       <c r="J69" s="6"/>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <v>46034</v>
       </c>
@@ -2961,7 +2969,7 @@
       </c>
       <c r="J70" s="6"/>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>46036</v>
       </c>
@@ -2989,7 +2997,7 @@
       </c>
       <c r="J71" s="6"/>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>46038</v>
       </c>
@@ -3015,7 +3023,7 @@
       </c>
       <c r="J72" s="6"/>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>46032</v>
       </c>
@@ -3043,7 +3051,7 @@
       </c>
       <c r="J73" s="6"/>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>46043</v>
       </c>
@@ -3071,7 +3079,7 @@
       </c>
       <c r="J74" s="6"/>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>46060</v>
       </c>
@@ -3099,7 +3107,7 @@
       </c>
       <c r="J75" s="6"/>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>46045</v>
       </c>
@@ -3127,7 +3135,7 @@
       </c>
       <c r="J76" s="6"/>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>46058</v>
       </c>
@@ -3153,7 +3161,7 @@
       </c>
       <c r="J77" s="6"/>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>46083</v>
       </c>
@@ -3181,7 +3189,7 @@
       </c>
       <c r="J78" s="6"/>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>46107</v>
       </c>
@@ -3207,7 +3215,7 @@
       </c>
       <c r="J79" s="6"/>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>46120</v>
       </c>
@@ -3235,7 +3243,7 @@
       </c>
       <c r="J80" s="6"/>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>46090</v>
       </c>
@@ -3263,7 +3271,7 @@
       </c>
       <c r="J81" s="6"/>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>46185</v>
       </c>
@@ -3289,7 +3297,7 @@
       </c>
       <c r="J82" s="6"/>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>46209</v>
       </c>
@@ -3317,7 +3325,7 @@
       </c>
       <c r="J83" s="6"/>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>46183</v>
       </c>
@@ -3345,7 +3353,7 @@
       </c>
       <c r="J84" s="6"/>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>46261</v>
       </c>
@@ -3373,7 +3381,7 @@
       </c>
       <c r="J85" s="6"/>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>46275</v>
       </c>
@@ -5038,2038 +5046,2074 @@
         <v>99</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="7"/>
-      <c r="H142" s="3"/>
-    </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" s="7">
+        <v>46318</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F142" s="1">
+        <v>74.61</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H142" s="3">
+        <v>621738.23999999999</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="7"/>
       <c r="H143" s="3"/>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="7"/>
       <c r="H144" s="3"/>
     </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="7"/>
       <c r="H145" s="3"/>
     </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="7"/>
       <c r="H146" s="3"/>
     </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="7"/>
       <c r="H147" s="3"/>
     </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="7"/>
       <c r="H148" s="3"/>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="7"/>
       <c r="H149" s="3"/>
     </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="7"/>
       <c r="H150" s="3"/>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="7"/>
       <c r="H151" s="3"/>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="7"/>
       <c r="H152" s="3"/>
     </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="7"/>
       <c r="H153" s="3"/>
     </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="7"/>
       <c r="H154" s="3"/>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="7"/>
       <c r="H155" s="3"/>
     </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="7"/>
       <c r="H156" s="3"/>
     </row>
-    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="7"/>
       <c r="H157" s="3"/>
     </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="7"/>
       <c r="H158" s="3"/>
     </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="7"/>
       <c r="H159" s="3"/>
     </row>
-    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="7"/>
       <c r="H160" s="3"/>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="7"/>
       <c r="H161" s="3"/>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="7"/>
       <c r="H162" s="3"/>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="7"/>
       <c r="H163" s="3"/>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="7"/>
       <c r="H164" s="3"/>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="7"/>
       <c r="H165" s="3"/>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="7"/>
       <c r="H166" s="3"/>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="7"/>
       <c r="H167" s="3"/>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="7"/>
       <c r="H168" s="3"/>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="7"/>
       <c r="H169" s="3"/>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="7"/>
       <c r="H170" s="3"/>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="7"/>
       <c r="H171" s="3"/>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="7"/>
       <c r="H172" s="3"/>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="7"/>
       <c r="H173" s="3"/>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="7"/>
       <c r="H174" s="3"/>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="7"/>
       <c r="H175" s="3"/>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="7"/>
       <c r="H176" s="3"/>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="7"/>
       <c r="H177" s="3"/>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="7"/>
       <c r="H178" s="3"/>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="7"/>
       <c r="H179" s="3"/>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="7"/>
       <c r="H180" s="3"/>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="7"/>
       <c r="H181" s="3"/>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="7"/>
       <c r="H182" s="3"/>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="7"/>
       <c r="H183" s="3"/>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="7"/>
       <c r="H184" s="3"/>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="7"/>
       <c r="H185" s="3"/>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="7"/>
       <c r="H186" s="3"/>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="7"/>
       <c r="H187" s="3"/>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="7"/>
       <c r="H188" s="3"/>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="7"/>
       <c r="H189" s="3"/>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="7"/>
       <c r="H190" s="3"/>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="7"/>
       <c r="H191" s="3"/>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="7"/>
       <c r="H192" s="3"/>
     </row>
-    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="7"/>
       <c r="H193" s="3"/>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="7"/>
       <c r="H194" s="3"/>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="7"/>
       <c r="H195" s="3"/>
     </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="7"/>
       <c r="H196" s="3"/>
     </row>
-    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="7"/>
       <c r="H197" s="3"/>
     </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="7"/>
       <c r="H198" s="3"/>
     </row>
-    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="7"/>
       <c r="H199" s="3"/>
     </row>
-    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="7"/>
       <c r="H200" s="3"/>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="7"/>
       <c r="H201" s="3"/>
     </row>
-    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="7"/>
       <c r="H202" s="3"/>
     </row>
-    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="7"/>
       <c r="H203" s="3"/>
     </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="7"/>
       <c r="H204" s="3"/>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="7"/>
       <c r="H205" s="3"/>
     </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="7"/>
       <c r="H206" s="3"/>
     </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="7"/>
       <c r="H207" s="3"/>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="7"/>
       <c r="H208" s="3"/>
     </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="7"/>
       <c r="H209" s="3"/>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="7"/>
       <c r="H210" s="3"/>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="7"/>
       <c r="H211" s="3"/>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="7"/>
       <c r="H212" s="3"/>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="7"/>
       <c r="H213" s="3"/>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="7"/>
       <c r="H214" s="3"/>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="7"/>
       <c r="H215" s="3"/>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="7"/>
       <c r="H216" s="3"/>
     </row>
-    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="7"/>
       <c r="H217" s="3"/>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="7"/>
       <c r="H218" s="3"/>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="7"/>
       <c r="H219" s="3"/>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="7"/>
       <c r="H220" s="3"/>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="7"/>
       <c r="H221" s="3"/>
     </row>
-    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="7"/>
       <c r="H222" s="3"/>
     </row>
-    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="7"/>
       <c r="H223" s="3"/>
     </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="7"/>
       <c r="H224" s="3"/>
     </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="7"/>
       <c r="H225" s="3"/>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="7"/>
       <c r="H226" s="3"/>
     </row>
-    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="7"/>
       <c r="H227" s="3"/>
     </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="7"/>
       <c r="H228" s="3"/>
     </row>
-    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="7"/>
       <c r="H229" s="3"/>
     </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="7"/>
       <c r="H230" s="3"/>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="7"/>
       <c r="H231" s="3"/>
     </row>
-    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="7"/>
       <c r="H232" s="3"/>
     </row>
-    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="7"/>
       <c r="H233" s="3"/>
     </row>
-    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="7"/>
       <c r="H234" s="3"/>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="7"/>
       <c r="H235" s="3"/>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="7"/>
       <c r="H236" s="3"/>
     </row>
-    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="7"/>
       <c r="H237" s="3"/>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="7"/>
       <c r="H238" s="3"/>
     </row>
-    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="7"/>
       <c r="H239" s="3"/>
     </row>
-    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="7"/>
       <c r="H240" s="3"/>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="7"/>
       <c r="H241" s="3"/>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="7"/>
       <c r="H242" s="3"/>
     </row>
-    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="7"/>
       <c r="H243" s="3"/>
     </row>
-    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="7"/>
       <c r="H244" s="3"/>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="7"/>
       <c r="H245" s="3"/>
     </row>
-    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="7"/>
       <c r="H246" s="3"/>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="7"/>
       <c r="H247" s="3"/>
     </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="7"/>
       <c r="H248" s="3"/>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="7"/>
       <c r="H249" s="3"/>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="7"/>
       <c r="H250" s="3"/>
     </row>
-    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="7"/>
       <c r="H251" s="3"/>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="7"/>
       <c r="H252" s="3"/>
     </row>
-    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="7"/>
       <c r="H253" s="3"/>
     </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="7"/>
       <c r="H254" s="3"/>
     </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="7"/>
       <c r="H255" s="3"/>
     </row>
-    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="7"/>
       <c r="H256" s="3"/>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="7"/>
       <c r="H257" s="3"/>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="7"/>
       <c r="H258" s="3"/>
     </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="7"/>
       <c r="H259" s="3"/>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="7"/>
       <c r="H260" s="3"/>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="7"/>
       <c r="H261" s="3"/>
     </row>
-    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="7"/>
       <c r="H262" s="3"/>
     </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="7"/>
       <c r="H263" s="3"/>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="7"/>
       <c r="H264" s="3"/>
     </row>
-    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="7"/>
       <c r="H265" s="3"/>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="7"/>
       <c r="H266" s="3"/>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="7"/>
       <c r="H267" s="3"/>
     </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="7"/>
       <c r="H268" s="3"/>
     </row>
-    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="7"/>
       <c r="H269" s="3"/>
     </row>
-    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="7"/>
       <c r="H270" s="3"/>
     </row>
-    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="7"/>
       <c r="H271" s="3"/>
     </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="7"/>
       <c r="H272" s="3"/>
     </row>
-    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="7"/>
       <c r="H273" s="3"/>
     </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="7"/>
       <c r="H274" s="3"/>
     </row>
-    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="7"/>
       <c r="H275" s="3"/>
     </row>
-    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="7"/>
       <c r="H276" s="3"/>
     </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="7"/>
       <c r="H277" s="3"/>
     </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="7"/>
       <c r="H278" s="3"/>
     </row>
-    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="7"/>
       <c r="H279" s="3"/>
     </row>
-    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="7"/>
       <c r="H280" s="3"/>
     </row>
-    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="7"/>
       <c r="H281" s="3"/>
     </row>
-    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="7"/>
       <c r="H282" s="3"/>
     </row>
-    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="7"/>
       <c r="H283" s="3"/>
     </row>
-    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="7"/>
       <c r="H284" s="3"/>
     </row>
-    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="7"/>
       <c r="H285" s="3"/>
     </row>
-    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="7"/>
       <c r="H286" s="3"/>
     </row>
-    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="7"/>
       <c r="H287" s="3"/>
     </row>
-    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="7"/>
       <c r="H288" s="3"/>
     </row>
-    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="7"/>
       <c r="H289" s="3"/>
     </row>
-    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="7"/>
       <c r="H290" s="3"/>
     </row>
-    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="7"/>
       <c r="H291" s="3"/>
     </row>
-    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="7"/>
       <c r="H292" s="3"/>
     </row>
-    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="7"/>
       <c r="H293" s="3"/>
     </row>
-    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="7"/>
       <c r="H294" s="3"/>
     </row>
-    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="7"/>
       <c r="H295" s="3"/>
     </row>
-    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="7"/>
       <c r="H296" s="3"/>
     </row>
-    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="7"/>
       <c r="H297" s="3"/>
     </row>
-    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="7"/>
       <c r="H298" s="3"/>
     </row>
-    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="7"/>
       <c r="H299" s="3"/>
     </row>
-    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="7"/>
       <c r="H300" s="3"/>
     </row>
-    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="7"/>
       <c r="H301" s="3"/>
     </row>
-    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="7"/>
       <c r="H302" s="3"/>
     </row>
-    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="7"/>
       <c r="H303" s="3"/>
     </row>
-    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="7"/>
       <c r="H304" s="3"/>
     </row>
-    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="7"/>
       <c r="H305" s="3"/>
     </row>
-    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="7"/>
       <c r="H306" s="3"/>
     </row>
-    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="7"/>
       <c r="H307" s="3"/>
     </row>
-    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="7"/>
       <c r="H308" s="3"/>
     </row>
-    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="7"/>
       <c r="H309" s="3"/>
     </row>
-    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="7"/>
       <c r="H310" s="3"/>
     </row>
-    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="7"/>
       <c r="H311" s="3"/>
     </row>
-    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="7"/>
       <c r="H312" s="3"/>
     </row>
-    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="7"/>
       <c r="H313" s="3"/>
     </row>
-    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="7"/>
       <c r="H314" s="3"/>
     </row>
-    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="7"/>
       <c r="H315" s="3"/>
     </row>
-    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="7"/>
       <c r="H316" s="3"/>
     </row>
-    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="7"/>
       <c r="H317" s="3"/>
     </row>
-    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="7"/>
       <c r="H318" s="3"/>
     </row>
-    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="7"/>
       <c r="H319" s="3"/>
     </row>
-    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="7"/>
       <c r="H320" s="3"/>
     </row>
-    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="7"/>
       <c r="H321" s="3"/>
     </row>
-    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="7"/>
       <c r="H322" s="3"/>
     </row>
-    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="7"/>
       <c r="H323" s="3"/>
     </row>
-    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="7"/>
       <c r="H324" s="3"/>
     </row>
-    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="7"/>
       <c r="H325" s="3"/>
     </row>
-    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="7"/>
       <c r="H326" s="3"/>
     </row>
-    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="7"/>
       <c r="H327" s="3"/>
     </row>
-    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="7"/>
       <c r="H328" s="3"/>
     </row>
-    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="7"/>
       <c r="H329" s="3"/>
     </row>
-    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="7"/>
       <c r="H330" s="3"/>
     </row>
-    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="7"/>
       <c r="H331" s="3"/>
     </row>
-    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="7"/>
       <c r="H332" s="3"/>
     </row>
-    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="7"/>
       <c r="H333" s="3"/>
     </row>
-    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="7"/>
       <c r="H334" s="3"/>
     </row>
-    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="7"/>
       <c r="H335" s="3"/>
     </row>
-    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="7"/>
       <c r="H336" s="3"/>
     </row>
-    <row r="337" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="7"/>
       <c r="H337" s="3"/>
     </row>
-    <row r="338" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="7"/>
       <c r="H338" s="3"/>
     </row>
-    <row r="339" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="7"/>
       <c r="H339" s="3"/>
     </row>
-    <row r="340" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="7"/>
       <c r="H340" s="3"/>
     </row>
-    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="7"/>
       <c r="H341" s="3"/>
     </row>
-    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="7"/>
       <c r="H342" s="3"/>
     </row>
-    <row r="343" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="7"/>
       <c r="H343" s="3"/>
     </row>
-    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="7"/>
       <c r="H344" s="3"/>
     </row>
-    <row r="345" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="7"/>
       <c r="H345" s="3"/>
     </row>
-    <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="7"/>
       <c r="H346" s="3"/>
     </row>
-    <row r="347" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" s="7"/>
       <c r="H347" s="3"/>
     </row>
-    <row r="348" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" s="7"/>
       <c r="H348" s="3"/>
     </row>
-    <row r="349" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" s="7"/>
       <c r="H349" s="3"/>
     </row>
-    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="7"/>
       <c r="H350" s="3"/>
     </row>
-    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="7"/>
       <c r="H351" s="3"/>
     </row>
-    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="7"/>
       <c r="H352" s="3"/>
     </row>
-    <row r="353" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" s="7"/>
       <c r="H353" s="3"/>
     </row>
-    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="7"/>
       <c r="H354" s="3"/>
     </row>
-    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" s="7"/>
       <c r="H355" s="3"/>
     </row>
-    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" s="7"/>
       <c r="H356" s="3"/>
     </row>
-    <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" s="7"/>
       <c r="H357" s="3"/>
     </row>
-    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" s="7"/>
       <c r="H358" s="3"/>
     </row>
-    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="7"/>
       <c r="H359" s="3"/>
     </row>
-    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" s="7"/>
       <c r="H360" s="3"/>
     </row>
-    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" s="7"/>
       <c r="H361" s="3"/>
     </row>
-    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" s="7"/>
       <c r="H362" s="3"/>
     </row>
-    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" s="7"/>
       <c r="H363" s="3"/>
     </row>
-    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" s="7"/>
       <c r="H364" s="3"/>
     </row>
-    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" s="7"/>
       <c r="H365" s="3"/>
     </row>
-    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" s="7"/>
       <c r="H366" s="3"/>
     </row>
-    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" s="7"/>
       <c r="H367" s="3"/>
     </row>
-    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" s="7"/>
       <c r="H368" s="3"/>
     </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="7"/>
       <c r="H369" s="3"/>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="7"/>
       <c r="H370" s="3"/>
     </row>
-    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" s="7"/>
       <c r="H371" s="3"/>
     </row>
-    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" s="7"/>
       <c r="H372" s="3"/>
     </row>
-    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" s="7"/>
       <c r="H373" s="3"/>
     </row>
-    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" s="7"/>
       <c r="H374" s="3"/>
     </row>
-    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" s="7"/>
       <c r="H375" s="3"/>
     </row>
-    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" s="7"/>
       <c r="H376" s="3"/>
     </row>
-    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" s="7"/>
       <c r="H377" s="3"/>
     </row>
-    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" s="7"/>
       <c r="H378" s="3"/>
     </row>
-    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" s="7"/>
       <c r="H379" s="3"/>
     </row>
-    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" s="7"/>
       <c r="H380" s="3"/>
     </row>
-    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" s="7"/>
       <c r="H381" s="3"/>
     </row>
-    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" s="7"/>
       <c r="H382" s="3"/>
     </row>
-    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" s="7"/>
       <c r="H383" s="3"/>
     </row>
-    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" s="7"/>
       <c r="H384" s="3"/>
     </row>
-    <row r="385" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="7"/>
       <c r="H385" s="3"/>
     </row>
-    <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" s="7"/>
       <c r="H386" s="3"/>
     </row>
-    <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" s="7"/>
       <c r="H387" s="3"/>
     </row>
-    <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" s="7"/>
       <c r="H388" s="3"/>
     </row>
-    <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" s="7"/>
       <c r="H389" s="3"/>
     </row>
-    <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" s="7"/>
       <c r="H390" s="3"/>
     </row>
-    <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" s="7"/>
       <c r="H391" s="3"/>
     </row>
-    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" s="7"/>
       <c r="H392" s="3"/>
     </row>
-    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" s="7"/>
       <c r="H393" s="3"/>
     </row>
-    <row r="394" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" s="7"/>
       <c r="H394" s="3"/>
     </row>
-    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" s="7"/>
       <c r="H395" s="3"/>
     </row>
-    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" s="7"/>
       <c r="H396" s="3"/>
     </row>
-    <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" s="7"/>
       <c r="H397" s="3"/>
     </row>
-    <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" s="7"/>
       <c r="H398" s="3"/>
     </row>
-    <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" s="7"/>
       <c r="H399" s="3"/>
     </row>
-    <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" s="7"/>
       <c r="H400" s="3"/>
     </row>
-    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" s="7"/>
       <c r="H401" s="3"/>
     </row>
-    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" s="7"/>
       <c r="H402" s="3"/>
     </row>
-    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" s="7"/>
       <c r="H403" s="3"/>
     </row>
-    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" s="7"/>
       <c r="H404" s="3"/>
     </row>
-    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" s="7"/>
       <c r="H405" s="3"/>
     </row>
-    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" s="7"/>
       <c r="H406" s="3"/>
     </row>
-    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" s="7"/>
       <c r="H407" s="3"/>
     </row>
-    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" s="7"/>
       <c r="H408" s="3"/>
     </row>
-    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" s="7"/>
       <c r="H409" s="3"/>
     </row>
-    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" s="7"/>
       <c r="H410" s="3"/>
     </row>
-    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" s="7"/>
       <c r="H411" s="3"/>
     </row>
-    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" s="7"/>
       <c r="H412" s="3"/>
     </row>
-    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" s="7"/>
       <c r="H413" s="3"/>
     </row>
-    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" s="7"/>
       <c r="H414" s="3"/>
     </row>
-    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" s="7"/>
       <c r="H415" s="3"/>
     </row>
-    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" s="7"/>
       <c r="H416" s="3"/>
     </row>
-    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" s="7"/>
       <c r="H417" s="3"/>
     </row>
-    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" s="7"/>
       <c r="H418" s="3"/>
     </row>
-    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" s="7"/>
       <c r="H419" s="3"/>
     </row>
-    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" s="7"/>
       <c r="H420" s="3"/>
     </row>
-    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" s="7"/>
       <c r="H421" s="3"/>
     </row>
-    <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" s="7"/>
       <c r="H422" s="3"/>
     </row>
-    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" s="7"/>
       <c r="H423" s="3"/>
     </row>
-    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" s="7"/>
       <c r="H424" s="3"/>
     </row>
-    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" s="7"/>
       <c r="H425" s="3"/>
     </row>
-    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" s="7"/>
       <c r="H426" s="3"/>
     </row>
-    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" s="7"/>
       <c r="H427" s="3"/>
     </row>
-    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" s="7"/>
       <c r="H428" s="3"/>
     </row>
-    <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" s="7"/>
       <c r="H429" s="3"/>
     </row>
-    <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" s="7"/>
       <c r="H430" s="3"/>
     </row>
-    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" s="7"/>
       <c r="H431" s="3"/>
     </row>
-    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" s="7"/>
       <c r="H432" s="3"/>
     </row>
-    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" s="7"/>
       <c r="H433" s="3"/>
     </row>
-    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" s="7"/>
       <c r="H434" s="3"/>
     </row>
-    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" s="7"/>
       <c r="H435" s="3"/>
     </row>
-    <row r="436" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" s="7"/>
       <c r="H436" s="3"/>
     </row>
-    <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" s="7"/>
       <c r="H437" s="3"/>
     </row>
-    <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" s="7"/>
       <c r="H438" s="3"/>
     </row>
-    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" s="7"/>
       <c r="H439" s="3"/>
     </row>
-    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" s="7"/>
       <c r="H440" s="3"/>
     </row>
-    <row r="441" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" s="7"/>
       <c r="H441" s="3"/>
     </row>
-    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" s="7"/>
       <c r="H442" s="3"/>
     </row>
-    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" s="7"/>
       <c r="H443" s="3"/>
     </row>
-    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" s="7"/>
       <c r="H444" s="3"/>
     </row>
-    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" s="7"/>
       <c r="H445" s="3"/>
     </row>
-    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" s="7"/>
       <c r="H446" s="3"/>
     </row>
-    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" s="7"/>
       <c r="H447" s="3"/>
     </row>
-    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" s="7"/>
       <c r="H448" s="3"/>
     </row>
-    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" s="7"/>
       <c r="H449" s="3"/>
     </row>
-    <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" s="7"/>
       <c r="H450" s="3"/>
     </row>
-    <row r="451" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" s="7"/>
       <c r="H451" s="3"/>
     </row>
-    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" s="7"/>
       <c r="H452" s="3"/>
     </row>
-    <row r="453" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" s="7"/>
       <c r="H453" s="3"/>
     </row>
-    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" s="7"/>
       <c r="H454" s="3"/>
     </row>
-    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" s="7"/>
       <c r="H455" s="3"/>
     </row>
-    <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" s="7"/>
       <c r="H456" s="3"/>
     </row>
-    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" s="7"/>
       <c r="H457" s="3"/>
     </row>
-    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" s="7"/>
       <c r="H458" s="3"/>
     </row>
-    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" s="7"/>
       <c r="H459" s="3"/>
     </row>
-    <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" s="7"/>
       <c r="H460" s="3"/>
     </row>
-    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" s="7"/>
       <c r="H461" s="3"/>
     </row>
-    <row r="462" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" s="7"/>
       <c r="H462" s="3"/>
     </row>
-    <row r="463" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" s="7"/>
       <c r="H463" s="3"/>
     </row>
-    <row r="464" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" s="7"/>
       <c r="H464" s="3"/>
     </row>
-    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" s="7"/>
       <c r="H465" s="3"/>
     </row>
-    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" s="7"/>
       <c r="H466" s="3"/>
     </row>
-    <row r="467" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" s="7"/>
       <c r="H467" s="3"/>
     </row>
-    <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" s="7"/>
       <c r="H468" s="3"/>
     </row>
-    <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" s="7"/>
       <c r="H469" s="3"/>
     </row>
-    <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" s="7"/>
       <c r="H470" s="3"/>
     </row>
-    <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" s="7"/>
       <c r="H471" s="3"/>
     </row>
-    <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" s="7"/>
       <c r="H472" s="3"/>
     </row>
-    <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" s="7"/>
       <c r="H473" s="3"/>
     </row>
-    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" s="7"/>
       <c r="H474" s="3"/>
     </row>
-    <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" s="7"/>
       <c r="H475" s="3"/>
     </row>
-    <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" s="7"/>
       <c r="H476" s="3"/>
     </row>
-    <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" s="7"/>
       <c r="H477" s="3"/>
     </row>
-    <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" s="7"/>
       <c r="H478" s="3"/>
     </row>
-    <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" s="7"/>
       <c r="H479" s="3"/>
     </row>
-    <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="7"/>
       <c r="H480" s="3"/>
     </row>
-    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" s="7"/>
       <c r="H481" s="3"/>
     </row>
-    <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" s="7"/>
       <c r="H482" s="3"/>
     </row>
-    <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" s="7"/>
       <c r="H483" s="3"/>
     </row>
-    <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" s="7"/>
       <c r="H484" s="3"/>
     </row>
-    <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" s="7"/>
       <c r="H485" s="3"/>
     </row>
-    <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" s="7"/>
       <c r="H486" s="3"/>
     </row>
-    <row r="487" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" s="7"/>
       <c r="H487" s="3"/>
     </row>
-    <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" s="7"/>
       <c r="H488" s="3"/>
     </row>
-    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" s="7"/>
       <c r="H489" s="3"/>
     </row>
-    <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" s="7"/>
       <c r="H490" s="3"/>
     </row>
-    <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" s="7"/>
       <c r="H491" s="3"/>
     </row>
-    <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" s="7"/>
       <c r="H492" s="3"/>
     </row>
-    <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" s="7"/>
       <c r="H493" s="3"/>
     </row>
-    <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" s="7"/>
       <c r="H494" s="3"/>
     </row>
-    <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" s="7"/>
       <c r="H495" s="3"/>
     </row>
-    <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" s="7"/>
       <c r="H496" s="3"/>
     </row>
-    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" s="7"/>
       <c r="H497" s="3"/>
     </row>
-    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" s="7"/>
       <c r="H498" s="3"/>
     </row>
-    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" s="7"/>
       <c r="H499" s="3"/>
     </row>
-    <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" s="7"/>
       <c r="H500" s="3"/>
     </row>
-    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" s="7"/>
       <c r="H501" s="3"/>
     </row>
-    <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" s="7"/>
       <c r="H502" s="3"/>
     </row>
-    <row r="503" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" s="7"/>
       <c r="H503" s="3"/>
     </row>
-    <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" s="7"/>
       <c r="H504" s="3"/>
     </row>
-    <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" s="7"/>
       <c r="H505" s="3"/>
     </row>
-    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" s="7"/>
       <c r="H506" s="3"/>
     </row>
-    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" s="7"/>
       <c r="H507" s="3"/>
     </row>
-    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" s="7"/>
       <c r="H508" s="3"/>
     </row>
-    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" s="7"/>
       <c r="H509" s="3"/>
     </row>
-    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" s="7"/>
       <c r="H510" s="3"/>
     </row>
-    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" s="7"/>
       <c r="H511" s="3"/>
     </row>
-    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" s="7"/>
       <c r="H512" s="3"/>
     </row>
-    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="7"/>
       <c r="H513" s="3"/>
     </row>
-    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="7"/>
       <c r="H514" s="3"/>
     </row>
-    <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="7"/>
       <c r="H515" s="3"/>
     </row>
-    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="7"/>
       <c r="H516" s="3"/>
     </row>
-    <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="7"/>
       <c r="H517" s="3"/>
     </row>
-    <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="7"/>
       <c r="H518" s="3"/>
     </row>
-    <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="7"/>
       <c r="H519" s="3"/>
     </row>
-    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="7"/>
       <c r="H520" s="3"/>
     </row>
-    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="7"/>
       <c r="H521" s="3"/>
     </row>
-    <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="7"/>
       <c r="H522" s="3"/>
     </row>
-    <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="7"/>
       <c r="H523" s="3"/>
     </row>
-    <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="7"/>
       <c r="H524" s="3"/>
     </row>
-    <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="7"/>
       <c r="H525" s="3"/>
     </row>
-    <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" s="7"/>
       <c r="H526" s="3"/>
     </row>
-    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" s="7"/>
       <c r="H527" s="3"/>
     </row>
-    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" s="7"/>
       <c r="H528" s="3"/>
     </row>
-    <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" s="7"/>
       <c r="H529" s="3"/>
     </row>
-    <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" s="7"/>
       <c r="H530" s="3"/>
     </row>
-    <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" s="7"/>
       <c r="H531" s="3"/>
     </row>
-    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" s="7"/>
       <c r="H532" s="3"/>
     </row>
-    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" s="7"/>
       <c r="H533" s="3"/>
     </row>
-    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" s="7"/>
       <c r="H534" s="3"/>
     </row>
-    <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" s="7"/>
       <c r="H535" s="3"/>
     </row>
-    <row r="536" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" s="7"/>
       <c r="H536" s="3"/>
     </row>
-    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" s="7"/>
       <c r="H537" s="3"/>
     </row>
-    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" s="7"/>
       <c r="H538" s="3"/>
     </row>
-    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" s="7"/>
       <c r="H539" s="3"/>
     </row>
-    <row r="540" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" s="7"/>
       <c r="H540" s="3"/>
     </row>
-    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" s="7"/>
       <c r="H541" s="3"/>
     </row>
-    <row r="542" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" s="7"/>
       <c r="H542" s="3"/>
     </row>
-    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" s="7"/>
       <c r="H543" s="3"/>
     </row>
-    <row r="544" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" s="7"/>
       <c r="H544" s="3"/>
     </row>
-    <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" s="7"/>
       <c r="H545" s="3"/>
     </row>
-    <row r="546" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" s="7"/>
       <c r="H546" s="3"/>
     </row>
-    <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" s="7"/>
       <c r="H547" s="3"/>
     </row>
-    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" s="7"/>
       <c r="H548" s="3"/>
     </row>
-    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" s="7"/>
       <c r="H549" s="3"/>
     </row>
-    <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" s="7"/>
       <c r="H550" s="3"/>
     </row>
-    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" s="7"/>
       <c r="H551" s="3"/>
     </row>
-    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" s="7"/>
       <c r="H552" s="3"/>
     </row>
-    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" s="7"/>
       <c r="H553" s="3"/>
     </row>
-    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" s="7"/>
       <c r="H554" s="3"/>
     </row>
-    <row r="555" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" s="7"/>
       <c r="H555" s="3"/>
     </row>
-    <row r="556" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" s="7"/>
       <c r="H556" s="3"/>
     </row>
-    <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" s="7"/>
       <c r="H557" s="3"/>
     </row>
-    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" s="7"/>
       <c r="H558" s="3"/>
     </row>
-    <row r="559" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" s="7"/>
       <c r="H559" s="3"/>
     </row>
-    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" s="7"/>
       <c r="H560" s="3"/>
     </row>
-    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" s="7"/>
       <c r="H561" s="3"/>
     </row>
-    <row r="562" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" s="7"/>
       <c r="H562" s="3"/>
     </row>
-    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" s="7"/>
       <c r="H563" s="3"/>
     </row>
-    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" s="7"/>
       <c r="H564" s="3"/>
     </row>
-    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" s="7"/>
       <c r="H565" s="3"/>
     </row>
-    <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" s="7"/>
       <c r="H566" s="3"/>
     </row>
-    <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" s="7"/>
       <c r="H567" s="3"/>
     </row>
-    <row r="568" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" s="7"/>
       <c r="H568" s="3"/>
     </row>
-    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" s="7"/>
       <c r="H569" s="3"/>
     </row>
-    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" s="7"/>
       <c r="H570" s="3"/>
     </row>
-    <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" s="7"/>
       <c r="H571" s="3"/>
     </row>
-    <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" s="7"/>
       <c r="H572" s="3"/>
     </row>
-    <row r="573" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" s="7"/>
       <c r="H573" s="3"/>
     </row>
-    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" s="7"/>
       <c r="H574" s="3"/>
     </row>
-    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" s="7"/>
       <c r="H575" s="3"/>
     </row>
-    <row r="576" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" s="7"/>
       <c r="H576" s="3"/>
     </row>
-    <row r="577" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" s="7"/>
       <c r="H577" s="3"/>
     </row>
-    <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" s="7"/>
       <c r="H578" s="3"/>
     </row>
-    <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" s="7"/>
       <c r="H579" s="3"/>
     </row>
-    <row r="580" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" s="7"/>
       <c r="H580" s="3"/>
     </row>
-    <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" s="7"/>
       <c r="H581" s="3"/>
     </row>
-    <row r="582" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" s="7"/>
       <c r="H582" s="3"/>
     </row>
-    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" s="7"/>
       <c r="H583" s="3"/>
     </row>
-    <row r="584" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" s="7"/>
       <c r="H584" s="3"/>
     </row>
-    <row r="585" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" s="7"/>
       <c r="H585" s="3"/>
     </row>
-    <row r="586" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" s="7"/>
       <c r="H586" s="3"/>
     </row>
-    <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" s="7"/>
       <c r="H587" s="3"/>
     </row>
-    <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" s="7"/>
       <c r="H588" s="3"/>
     </row>
-    <row r="589" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" s="7"/>
       <c r="H589" s="3"/>
     </row>
-    <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" s="7"/>
       <c r="H590" s="3"/>
     </row>
-    <row r="591" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" s="7"/>
       <c r="H591" s="3"/>
     </row>
-    <row r="592" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A592" s="7"/>
       <c r="H592" s="3"/>
     </row>
-    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" s="7"/>
       <c r="H593" s="3"/>
     </row>
-    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A594" s="7"/>
       <c r="H594" s="3"/>
     </row>
-    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A595" s="7"/>
       <c r="H595" s="3"/>
     </row>
-    <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A596" s="7"/>
       <c r="H596" s="3"/>
     </row>
-    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" s="7"/>
       <c r="H597" s="3"/>
     </row>
-    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A598" s="7"/>
       <c r="H598" s="3"/>
     </row>
-    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A599" s="7"/>
       <c r="H599" s="3"/>
     </row>
-    <row r="600" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A600" s="7"/>
       <c r="H600" s="3"/>
     </row>
-    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A601" s="7"/>
       <c r="H601" s="3"/>
     </row>
-    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A602" s="7"/>
       <c r="H602" s="3"/>
     </row>
-    <row r="603" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A603" s="7"/>
       <c r="H603" s="3"/>
     </row>
-    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A604" s="7"/>
       <c r="H604" s="3"/>
     </row>
-    <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" s="7"/>
       <c r="H605" s="3"/>
     </row>
-    <row r="606" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" s="7"/>
       <c r="H606" s="3"/>
     </row>
-    <row r="607" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" s="7"/>
       <c r="H607" s="3"/>
     </row>
-    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" s="7"/>
       <c r="H608" s="3"/>
     </row>
-    <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609" s="7"/>
       <c r="H609" s="3"/>
     </row>
-    <row r="610" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" s="7"/>
       <c r="H610" s="3"/>
     </row>
-    <row r="611" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" s="7"/>
       <c r="H611" s="3"/>
     </row>
-    <row r="612" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" s="7"/>
       <c r="H612" s="3"/>
     </row>
-    <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" s="7"/>
       <c r="H613" s="3"/>
     </row>
-    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" s="7"/>
       <c r="H614" s="3"/>
     </row>
-    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" s="7"/>
       <c r="H615" s="3"/>
     </row>
-    <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" s="7"/>
       <c r="H616" s="3"/>
     </row>
-    <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" s="7"/>
       <c r="H617" s="3"/>
     </row>
-    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" s="7"/>
       <c r="H618" s="3"/>
     </row>
-    <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" s="7"/>
       <c r="H619" s="3"/>
     </row>
-    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" s="7"/>
       <c r="H620" s="3"/>
     </row>
-    <row r="621" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" s="7"/>
       <c r="H621" s="3"/>
     </row>
-    <row r="622" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" s="7"/>
       <c r="H622" s="3"/>
     </row>
-    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" s="7"/>
       <c r="H623" s="3"/>
     </row>
-    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" s="7"/>
       <c r="H624" s="3"/>
     </row>
-    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" s="7"/>
       <c r="H625" s="3"/>
     </row>
-    <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" s="7"/>
       <c r="H626" s="3"/>
     </row>
-    <row r="627" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" s="7"/>
       <c r="H627" s="3"/>
     </row>
-    <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" s="7"/>
       <c r="H628" s="3"/>
     </row>
-    <row r="629" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" s="7"/>
       <c r="H629" s="3"/>
     </row>
-    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" s="7"/>
       <c r="H630" s="3"/>
     </row>
-    <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" s="7"/>
       <c r="H631" s="3"/>
     </row>
-    <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" s="7"/>
       <c r="H632" s="3"/>
     </row>
-    <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" s="7"/>
       <c r="H633" s="3"/>
     </row>
-    <row r="634" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" s="7"/>
       <c r="H634" s="3"/>
     </row>
-    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" s="7"/>
       <c r="H635" s="3"/>
     </row>
-    <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" s="7"/>
       <c r="H636" s="3"/>
     </row>
-    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" s="7"/>
       <c r="H637" s="3"/>
     </row>
-    <row r="638" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" s="7"/>
       <c r="H638" s="3"/>
     </row>
-    <row r="639" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" s="7"/>
       <c r="H639" s="3"/>
     </row>
-    <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" s="7"/>
       <c r="H640" s="3"/>
     </row>
-    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" s="7"/>
       <c r="H641" s="3"/>
     </row>
-    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" s="7"/>
       <c r="H642" s="3"/>
     </row>
-    <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" s="7"/>
       <c r="H643" s="3"/>
     </row>
-    <row r="644" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" s="7"/>
       <c r="H644" s="3"/>
     </row>
-    <row r="645" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A645" s="7"/>
       <c r="H645" s="3"/>
     </row>
-    <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" s="7"/>
       <c r="H646" s="3"/>
     </row>
-    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" s="7"/>
       <c r="H647" s="3"/>
     </row>
+    <row r="648" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A648" s="7">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="649" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A649" s="7"/>
+    </row>
+    <row r="650" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A650" s="7"/>
+    </row>
+    <row r="651" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A651" s="7"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I647" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Andrade Home Resort"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I648" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <ignoredErrors>
@@ -7077,7 +7121,7 @@
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{070D9A3B-D984-42A1-8AD7-CE92EBF09B76}">
           <x14:formula1>
             <xm:f>Corretores!$A$2:$A$25</xm:f>
